--- a/docs/design/ACSMS-SCR-019/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店Excelデータ取込画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-019/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店Excelデータ取込画面_V1.0.xlsx
@@ -1700,7 +1700,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2171,7 +2171,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3157,7 +3157,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3359,7 +3359,7 @@
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="19" t="inlineStr">
         <is>
-          <t>販売店Excelデータを一括取込する（新規登録 / 全項目更新 / 入力箇所のみ更新）。1トランザクションで処理し、エラー時は全件ロールバック。</t>
+          <t>販売店Excelデータを一括取込する（新規登録 / 更新）。`UPDATE` モードは selected_columns に含まれる列のみ更新し、未選択列は既存値を維持する（全項目更新したい場合は全列を selected_columns に含める。2026-07 顧客要件により旧 `UPDATE_ALL` / `UPDATE_PARTIAL` の2区分は `UPDATE` に統合済み）。1トランザクションで処理し、エラー時は全件ロールバック。</t>
         </is>
       </c>
       <c r="T7" s="10" t="n"/>
@@ -3592,7 +3592,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="C50" s="19" t="inlineStr">
         <is>
-          <t>手数料区分</t>
+          <t>振込手数料負担区分</t>
         </is>
       </c>
       <c r="D50" s="10" t="n"/>
@@ -5691,7 +5691,7 @@
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>手数料区分</t>
+          <t>振込手数料負担区分</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
@@ -5699,7 +5699,7 @@
       <c r="P50" s="11" t="n"/>
       <c r="Q50" s="17" t="inlineStr">
         <is>
-          <t>tesuryo_kubun</t>
+          <t>furikomi_tesuryo_futan_kubun</t>
         </is>
       </c>
       <c r="R50" s="10" t="n"/>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="C51" s="19" t="inlineStr">
         <is>
-          <t>手数料</t>
+          <t>振込手数料</t>
         </is>
       </c>
       <c r="D51" s="10" t="n"/>
@@ -5751,7 +5751,7 @@
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="17" t="inlineStr">
         <is>
-          <t>手数料金額</t>
+          <t>振込手数料</t>
         </is>
       </c>
       <c r="N51" s="10" t="n"/>
@@ -5759,7 +5759,7 @@
       <c r="P51" s="11" t="n"/>
       <c r="Q51" s="17" t="inlineStr">
         <is>
-          <t>tesuryo_amount</t>
+          <t>furikomi_tesuryo</t>
         </is>
       </c>
       <c r="R51" s="10" t="n"/>
@@ -6217,7 +6217,7 @@
     <row r="78" ht="36" customHeight="1">
       <c r="D78" s="38" t="inlineStr">
         <is>
-          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
     <row r="84" ht="72" customHeight="1">
       <c r="D84" s="38" t="inlineStr">
         <is>
-          <t>「販売店コード」「販売店名称」「販売店名称（カナ）」「インボイス番号」「郵便番号」「住所」「電話番号」「FAX番号」「所長名」「委託区分」「配達手数料単価」「金融機関コード」「金融機関名」「配達手数料支払サイクル」「口座支店コード」「口座支店名」「口座種別」「口座番号」「口座名義」「手数料区分」「手数料」「備考」「廃店フラグ」</t>
+          <t>「販売店コード」「販売店名称」「販売店名称（カナ）」「インボイス番号」「郵便番号」「住所」「電話番号」「FAX番号」「所長名」「委託区分」「配達手数料単価」「金融機関コード」「金融機関名」「配達手数料支払サイクル」「口座支店コード」「口座支店名」「口座種別」「口座番号」「口座名義」「振込手数料負担区分」「振込手数料」「備考」「廃店フラグ」</t>
         </is>
       </c>
     </row>
@@ -6593,7 +6593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK146"/>
+  <dimension ref="A1:AK147"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -6754,7 +6754,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -6863,7 +6863,7 @@
       <c r="AJ7" s="10" t="n"/>
       <c r="AK7" s="11" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="B8" s="33" t="inlineStr">
         <is>
           <t>概要</t>
@@ -6878,7 +6878,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>販売店Excelデータを一括取込する（新規登録 / 全項目更新 / 入力箇所のみ更新）。1トランザクションで処理し、エラー時は全件ロールバック。</t>
+          <t>販売店Excelデータを一括取込する（新規登録 / 更新）。`UPDATE` モードは selected_columns に含まれる列のみ更新し、未選択列は既存値を維持する（全項目更新したい場合は全列を selected_columns に含める。2026-07 顧客要件により旧 `UPDATE_ALL` / `UPDATE_PARTIAL` の2区分は `UPDATE` に統合済み）。1トランザクションで処理し、エラー時は全件ロールバック。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -7374,23 +7374,17 @@
       <c r="AK19" s="11" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="25" t="n"/>
-      <c r="G20" s="25" t="n"/>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="26" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="I20" s="36" t="n"/>
       <c r="J20" s="17" t="n">
-        <v>500</v>
+        <v>429</v>
       </c>
       <c r="K20" s="10" t="n"/>
       <c r="L20" s="10" t="n"/>
       <c r="M20" s="11" t="n"/>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>システムエラーが発生しました</t>
+          <t>リクエスト回数が上限を超えました</t>
         </is>
       </c>
       <c r="O20" s="10" t="n"/>
@@ -7417,92 +7411,68 @@
       <c r="AJ20" s="10" t="n"/>
       <c r="AK20" s="11" t="n"/>
     </row>
-    <row r="21" ht="19.5" customHeight="1"/>
-    <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="27" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+      <c r="G21" s="25" t="n"/>
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="26" t="n"/>
+      <c r="J21" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="10" t="n"/>
+      <c r="M21" s="11" t="n"/>
+      <c r="N21" s="19" t="inlineStr">
+        <is>
+          <t>システムエラーが発生しました</t>
+        </is>
+      </c>
+      <c r="O21" s="10" t="n"/>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="10" t="n"/>
+      <c r="R21" s="10" t="n"/>
+      <c r="S21" s="10" t="n"/>
+      <c r="T21" s="10" t="n"/>
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="10" t="n"/>
+      <c r="W21" s="10" t="n"/>
+      <c r="X21" s="10" t="n"/>
+      <c r="Y21" s="10" t="n"/>
+      <c r="Z21" s="10" t="n"/>
+      <c r="AA21" s="10" t="n"/>
+      <c r="AB21" s="10" t="n"/>
+      <c r="AC21" s="10" t="n"/>
+      <c r="AD21" s="10" t="n"/>
+      <c r="AE21" s="10" t="n"/>
+      <c r="AF21" s="10" t="n"/>
+      <c r="AG21" s="10" t="n"/>
+      <c r="AH21" s="10" t="n"/>
+      <c r="AI21" s="10" t="n"/>
+      <c r="AJ21" s="10" t="n"/>
+      <c r="AK21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="19.5" customHeight="1"/>
+    <row r="23" ht="19.5" customHeight="1">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>2. リクエストパラメータ</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="19.5" customHeight="1"/>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="B24" s="30" t="inlineStr">
+    <row r="24" ht="19.5" customHeight="1"/>
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>パラメーターID</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="10" t="n"/>
-      <c r="I24" s="10" t="n"/>
-      <c r="J24" s="10" t="n"/>
-      <c r="K24" s="10" t="n"/>
-      <c r="L24" s="11" t="n"/>
-      <c r="M24" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N24" s="10" t="n"/>
-      <c r="O24" s="10" t="n"/>
-      <c r="P24" s="11" t="n"/>
-      <c r="Q24" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R24" s="10" t="n"/>
-      <c r="S24" s="11" t="n"/>
-      <c r="T24" s="16" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="U24" s="10" t="n"/>
-      <c r="V24" s="10" t="n"/>
-      <c r="W24" s="10" t="n"/>
-      <c r="X24" s="11" t="n"/>
-      <c r="Y24" s="16" t="inlineStr">
-        <is>
-          <t>最小長</t>
-        </is>
-      </c>
-      <c r="Z24" s="10" t="n"/>
-      <c r="AA24" s="10" t="n"/>
-      <c r="AB24" s="11" t="n"/>
-      <c r="AC24" s="16" t="inlineStr">
-        <is>
-          <t>最大長</t>
-        </is>
-      </c>
-      <c r="AD24" s="10" t="n"/>
-      <c r="AE24" s="11" t="n"/>
-      <c r="AF24" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG24" s="10" t="n"/>
-      <c r="AH24" s="10" t="n"/>
-      <c r="AI24" s="10" t="n"/>
-      <c r="AJ24" s="10" t="n"/>
-      <c r="AK24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="36" customHeight="1">
-      <c r="B25" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>import_mode</t>
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
@@ -7514,40 +7484,48 @@
       <c r="J25" s="10" t="n"/>
       <c r="K25" s="10" t="n"/>
       <c r="L25" s="11" t="n"/>
-      <c r="M25" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N25" s="10" t="n"/>
       <c r="O25" s="10" t="n"/>
       <c r="P25" s="11" t="n"/>
-      <c r="Q25" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q25" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R25" s="10" t="n"/>
       <c r="S25" s="11" t="n"/>
-      <c r="T25" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
+      <c r="T25" s="16" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
       <c r="U25" s="10" t="n"/>
       <c r="V25" s="10" t="n"/>
       <c r="W25" s="10" t="n"/>
       <c r="X25" s="11" t="n"/>
-      <c r="Y25" s="17" t="inlineStr"/>
+      <c r="Y25" s="16" t="inlineStr">
+        <is>
+          <t>最小長</t>
+        </is>
+      </c>
       <c r="Z25" s="10" t="n"/>
       <c r="AA25" s="10" t="n"/>
       <c r="AB25" s="11" t="n"/>
-      <c r="AC25" s="17" t="inlineStr"/>
+      <c r="AC25" s="16" t="inlineStr">
+        <is>
+          <t>最大長</t>
+        </is>
+      </c>
       <c r="AD25" s="10" t="n"/>
       <c r="AE25" s="11" t="n"/>
-      <c r="AF25" s="19" t="inlineStr">
-        <is>
-          <t>取込モード（`NEW`:新規登録, `UPDATE_ALL`:全項目更新, `UPDATE_PARTIAL`:入力箇所のみ更新）</t>
+      <c r="AF25" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -7556,13 +7534,13 @@
       <c r="AJ25" s="10" t="n"/>
       <c r="AK25" s="11" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="B26" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>selected_columns</t>
+          <t>import_mode</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -7576,7 +7554,7 @@
       <c r="L26" s="11" t="n"/>
       <c r="M26" s="17" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N26" s="10" t="n"/>
@@ -7584,7 +7562,7 @@
       <c r="P26" s="11" t="n"/>
       <c r="Q26" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R26" s="10" t="n"/>
@@ -7598,20 +7576,16 @@
       <c r="V26" s="10" t="n"/>
       <c r="W26" s="10" t="n"/>
       <c r="X26" s="11" t="n"/>
-      <c r="Y26" s="17" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y26" s="17" t="inlineStr"/>
       <c r="Z26" s="10" t="n"/>
       <c r="AA26" s="10" t="n"/>
       <c r="AB26" s="11" t="n"/>
-      <c r="AC26" s="17" t="n">
-        <v>23</v>
-      </c>
+      <c r="AC26" s="17" t="inlineStr"/>
       <c r="AD26" s="10" t="n"/>
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>取込対象の列（物理カラム名）配列。hanbaiten_code は常に含む。</t>
+          <t>取込モード（`NEW`:新規登録, `UPDATE`:更新。selected_columns に含まれる列のみ更新し未選択列は既存値を維持する）</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -7622,11 +7596,11 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>rows</t>
+          <t>selected_columns</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -7669,13 +7643,13 @@
       <c r="AA27" s="10" t="n"/>
       <c r="AB27" s="11" t="n"/>
       <c r="AC27" s="17" t="n">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>取込データ行の配列</t>
+          <t>取込対象の列（物理カラム名）配列。hanbaiten_code は常に含む。</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -7686,11 +7660,11 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>→hanbaiten_code</t>
+          <t>rows</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -7704,7 +7678,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -7712,7 +7686,7 @@
       <c r="P28" s="11" t="n"/>
       <c r="Q28" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="R28" s="10" t="n"/>
@@ -7733,13 +7707,13 @@
       <c r="AA28" s="10" t="n"/>
       <c r="AB28" s="11" t="n"/>
       <c r="AC28" s="17" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="AD28" s="10" t="n"/>
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>販売店コード（行内必須、キー項目）</t>
+          <t>取込データ行の配列</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -7750,11 +7724,11 @@
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>→hanbaiten_name</t>
+          <t>→hanbaiten_code</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -7783,7 +7757,7 @@
       <c r="S29" s="11" t="n"/>
       <c r="T29" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="U29" s="10" t="n"/>
@@ -7797,13 +7771,13 @@
       <c r="AA29" s="10" t="n"/>
       <c r="AB29" s="11" t="n"/>
       <c r="AC29" s="17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="AD29" s="10" t="n"/>
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>販売店名</t>
+          <t>販売店コード（行内必須、キー項目）</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -7814,11 +7788,11 @@
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>→hanbaiten_name_kana</t>
+          <t>→hanbaiten_name</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -7867,7 +7841,7 @@
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>販売店名（カナ）</t>
+          <t>販売店名</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -7878,11 +7852,11 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>→torihikisaki_no</t>
+          <t>→hanbaiten_name_kana</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
@@ -7925,13 +7899,13 @@
       <c r="AA31" s="10" t="n"/>
       <c r="AB31" s="11" t="n"/>
       <c r="AC31" s="17" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AD31" s="10" t="n"/>
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>適格請求書発行事業者番号</t>
+          <t>販売店名（カナ）</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -7942,11 +7916,11 @@
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>→yubin_no</t>
+          <t>→torihikisaki_no</t>
         </is>
       </c>
       <c r="D32" s="10" t="n"/>
@@ -7983,19 +7957,19 @@
       <c r="W32" s="10" t="n"/>
       <c r="X32" s="11" t="n"/>
       <c r="Y32" s="17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="10" t="n"/>
       <c r="AA32" s="10" t="n"/>
       <c r="AB32" s="11" t="n"/>
       <c r="AC32" s="17" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AD32" s="10" t="n"/>
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>適格請求書発行事業者番号</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -8006,11 +7980,11 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>→address</t>
+          <t>→yubin_no</t>
         </is>
       </c>
       <c r="D33" s="10" t="n"/>
@@ -8047,19 +8021,19 @@
       <c r="W33" s="10" t="n"/>
       <c r="X33" s="11" t="n"/>
       <c r="Y33" s="17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z33" s="10" t="n"/>
       <c r="AA33" s="10" t="n"/>
       <c r="AB33" s="11" t="n"/>
       <c r="AC33" s="17" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="AD33" s="10" t="n"/>
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>住所</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -8070,11 +8044,11 @@
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>→tel</t>
+          <t>→address</t>
         </is>
       </c>
       <c r="D34" s="10" t="n"/>
@@ -8117,13 +8091,13 @@
       <c r="AA34" s="10" t="n"/>
       <c r="AB34" s="11" t="n"/>
       <c r="AC34" s="17" t="n">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="AD34" s="10" t="n"/>
       <c r="AE34" s="11" t="n"/>
       <c r="AF34" s="19" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -8134,11 +8108,11 @@
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>→fax</t>
+          <t>→tel</t>
         </is>
       </c>
       <c r="D35" s="10" t="n"/>
@@ -8187,7 +8161,7 @@
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>FAX番号</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -8198,11 +8172,11 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>→shocho_name</t>
+          <t>→fax</t>
         </is>
       </c>
       <c r="D36" s="10" t="n"/>
@@ -8245,13 +8219,13 @@
       <c r="AA36" s="10" t="n"/>
       <c r="AB36" s="11" t="n"/>
       <c r="AC36" s="17" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="AD36" s="10" t="n"/>
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>所長名</t>
+          <t>FAX番号</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -8262,11 +8236,11 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>→itaku_kubun</t>
+          <t>→shocho_name</t>
         </is>
       </c>
       <c r="D37" s="10" t="n"/>
@@ -8280,7 +8254,7 @@
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N37" s="10" t="n"/>
@@ -8302,20 +8276,20 @@
       <c r="V37" s="10" t="n"/>
       <c r="W37" s="10" t="n"/>
       <c r="X37" s="11" t="n"/>
-      <c r="Y37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y37" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="Z37" s="10" t="n"/>
       <c r="AA37" s="10" t="n"/>
       <c r="AB37" s="11" t="n"/>
-      <c r="AC37" s="17" t="inlineStr"/>
+      <c r="AC37" s="17" t="n">
+        <v>50</v>
+      </c>
       <c r="AD37" s="10" t="n"/>
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>委託区分（1:振込, 2:日農委託, 9:その他）</t>
+          <t>所長名</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -8326,11 +8300,11 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>→haitatsuryo_tanka_code</t>
+          <t>→itaku_kubun</t>
         </is>
       </c>
       <c r="D38" s="10" t="n"/>
@@ -8344,7 +8318,7 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
@@ -8366,20 +8340,20 @@
       <c r="V38" s="10" t="n"/>
       <c r="W38" s="10" t="n"/>
       <c r="X38" s="11" t="n"/>
-      <c r="Y38" s="17" t="n">
-        <v>1</v>
+      <c r="Y38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z38" s="10" t="n"/>
       <c r="AA38" s="10" t="n"/>
       <c r="AB38" s="11" t="n"/>
-      <c r="AC38" s="17" t="n">
-        <v>10</v>
-      </c>
+      <c r="AC38" s="17" t="inlineStr"/>
       <c r="AD38" s="10" t="n"/>
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>配達手数料単価コード（m_tanka の tanka_code で解決）</t>
+          <t>委託区分（1:振込, 2:日農委託, 9:その他）</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -8390,11 +8364,11 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t>→bank_code</t>
+          <t>→haitatsuryo_tanka_code</t>
         </is>
       </c>
       <c r="D39" s="10" t="n"/>
@@ -8437,13 +8411,13 @@
       <c r="AA39" s="10" t="n"/>
       <c r="AB39" s="11" t="n"/>
       <c r="AC39" s="17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AD39" s="10" t="n"/>
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>銀行コード</t>
+          <t>配達手数料単価コード（m_tanka の tanka_code で解決）</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -8454,11 +8428,11 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>→bank_name</t>
+          <t>→bank_code</t>
         </is>
       </c>
       <c r="D40" s="10" t="n"/>
@@ -8501,13 +8475,13 @@
       <c r="AA40" s="10" t="n"/>
       <c r="AB40" s="11" t="n"/>
       <c r="AC40" s="17" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="AD40" s="10" t="n"/>
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>銀行名</t>
+          <t>銀行コード</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -8518,11 +8492,11 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t>→haitatsuryo_shiharai_cycle</t>
+          <t>→bank_name</t>
         </is>
       </c>
       <c r="D41" s="10" t="n"/>
@@ -8536,7 +8510,7 @@
       <c r="L41" s="11" t="n"/>
       <c r="M41" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N41" s="10" t="n"/>
@@ -8558,20 +8532,20 @@
       <c r="V41" s="10" t="n"/>
       <c r="W41" s="10" t="n"/>
       <c r="X41" s="11" t="n"/>
-      <c r="Y41" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y41" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="Z41" s="10" t="n"/>
       <c r="AA41" s="10" t="n"/>
       <c r="AB41" s="11" t="n"/>
-      <c r="AC41" s="17" t="inlineStr"/>
+      <c r="AC41" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AD41" s="10" t="n"/>
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>配達手数料支払サイクル（月数）</t>
+          <t>銀行名</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -8582,11 +8556,11 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>→bank_branch_code</t>
+          <t>→haitatsuryo_shiharai_cycle</t>
         </is>
       </c>
       <c r="D42" s="10" t="n"/>
@@ -8600,7 +8574,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -8622,20 +8596,20 @@
       <c r="V42" s="10" t="n"/>
       <c r="W42" s="10" t="n"/>
       <c r="X42" s="11" t="n"/>
-      <c r="Y42" s="17" t="n">
-        <v>1</v>
+      <c r="Y42" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z42" s="10" t="n"/>
       <c r="AA42" s="10" t="n"/>
       <c r="AB42" s="11" t="n"/>
-      <c r="AC42" s="17" t="n">
-        <v>3</v>
-      </c>
+      <c r="AC42" s="17" t="inlineStr"/>
       <c r="AD42" s="10" t="n"/>
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>口座支店コード</t>
+          <t>配達手数料支払サイクル（月数）</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -8646,11 +8620,11 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t>→bank_branch_name</t>
+          <t>→bank_branch_code</t>
         </is>
       </c>
       <c r="D43" s="10" t="n"/>
@@ -8693,13 +8667,13 @@
       <c r="AA43" s="10" t="n"/>
       <c r="AB43" s="11" t="n"/>
       <c r="AC43" s="17" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="AD43" s="10" t="n"/>
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>口座支店名</t>
+          <t>口座支店コード</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -8710,11 +8684,11 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>→yokin_shubetsu</t>
+          <t>→bank_branch_name</t>
         </is>
       </c>
       <c r="D44" s="10" t="n"/>
@@ -8728,7 +8702,7 @@
       <c r="L44" s="11" t="n"/>
       <c r="M44" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N44" s="10" t="n"/>
@@ -8750,20 +8724,20 @@
       <c r="V44" s="10" t="n"/>
       <c r="W44" s="10" t="n"/>
       <c r="X44" s="11" t="n"/>
-      <c r="Y44" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y44" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="Z44" s="10" t="n"/>
       <c r="AA44" s="10" t="n"/>
       <c r="AB44" s="11" t="n"/>
-      <c r="AC44" s="17" t="inlineStr"/>
+      <c r="AC44" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AD44" s="10" t="n"/>
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>口座種別（1:普通, 2:当座）</t>
+          <t>口座支店名</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -8774,11 +8748,11 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>→koza_no</t>
+          <t>→yokin_shubetsu</t>
         </is>
       </c>
       <c r="D45" s="10" t="n"/>
@@ -8792,7 +8766,7 @@
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N45" s="10" t="n"/>
@@ -8814,20 +8788,20 @@
       <c r="V45" s="10" t="n"/>
       <c r="W45" s="10" t="n"/>
       <c r="X45" s="11" t="n"/>
-      <c r="Y45" s="17" t="n">
-        <v>1</v>
+      <c r="Y45" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Z45" s="10" t="n"/>
       <c r="AA45" s="10" t="n"/>
       <c r="AB45" s="11" t="n"/>
-      <c r="AC45" s="17" t="n">
-        <v>10</v>
-      </c>
+      <c r="AC45" s="17" t="inlineStr"/>
       <c r="AD45" s="10" t="n"/>
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>口座番号</t>
+          <t>口座種別（1:普通, 2:当座）</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -8838,11 +8812,11 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C46" s="19" t="inlineStr">
         <is>
-          <t>→koza_meigi</t>
+          <t>→koza_no</t>
         </is>
       </c>
       <c r="D46" s="10" t="n"/>
@@ -8885,13 +8859,13 @@
       <c r="AA46" s="10" t="n"/>
       <c r="AB46" s="11" t="n"/>
       <c r="AC46" s="17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="AD46" s="10" t="n"/>
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>口座名義</t>
+          <t>口座番号</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -8902,11 +8876,11 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C47" s="19" t="inlineStr">
         <is>
-          <t>→tesuryo_kubun</t>
+          <t>→koza_meigi</t>
         </is>
       </c>
       <c r="D47" s="10" t="n"/>
@@ -8920,7 +8894,7 @@
       <c r="L47" s="11" t="n"/>
       <c r="M47" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N47" s="10" t="n"/>
@@ -8942,20 +8916,20 @@
       <c r="V47" s="10" t="n"/>
       <c r="W47" s="10" t="n"/>
       <c r="X47" s="11" t="n"/>
-      <c r="Y47" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Y47" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="Z47" s="10" t="n"/>
       <c r="AA47" s="10" t="n"/>
       <c r="AB47" s="11" t="n"/>
-      <c r="AC47" s="17" t="inlineStr"/>
+      <c r="AC47" s="17" t="n">
+        <v>50</v>
+      </c>
       <c r="AD47" s="10" t="n"/>
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>手数料区分（1:JA, 2:販売店）</t>
+          <t>口座名義</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -8966,11 +8940,11 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>→tesuryo_amount</t>
+          <t>→furikomi_tesuryo_futan_kubun</t>
         </is>
       </c>
       <c r="D48" s="10" t="n"/>
@@ -9019,7 +8993,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>手数料（≧ 0）</t>
+          <t>振込手数料負担区分（1:JA, 2:販売店）</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -9030,11 +9004,11 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C49" s="19" t="inlineStr">
         <is>
-          <t>→biko</t>
+          <t>→furikomi_tesuryo</t>
         </is>
       </c>
       <c r="D49" s="10" t="n"/>
@@ -9048,7 +9022,7 @@
       <c r="L49" s="11" t="n"/>
       <c r="M49" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N49" s="10" t="n"/>
@@ -9083,7 +9057,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>振込手数料（≧ 0）</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -9094,11 +9068,11 @@
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C50" s="19" t="inlineStr">
         <is>
-          <t>→haiten_flg</t>
+          <t>→biko</t>
         </is>
       </c>
       <c r="D50" s="10" t="n"/>
@@ -9112,7 +9086,7 @@
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
@@ -9147,7 +9121,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>廃店フラグ（true:廃店, false:営業中）</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -9156,88 +9130,88 @@
       <c r="AJ50" s="10" t="n"/>
       <c r="AK50" s="11" t="n"/>
     </row>
-    <row r="51" ht="19.5" customHeight="1"/>
-    <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="27" t="inlineStr">
+    <row r="51" ht="18" customHeight="1">
+      <c r="B51" s="31" t="n">
+        <v>26</v>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>→haiten_flg</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="n"/>
+      <c r="J51" s="10" t="n"/>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="11" t="n"/>
+      <c r="M51" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="11" t="n"/>
+      <c r="T51" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="11" t="n"/>
+      <c r="Y51" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="11" t="n"/>
+      <c r="AC51" s="17" t="inlineStr"/>
+      <c r="AD51" s="10" t="n"/>
+      <c r="AE51" s="11" t="n"/>
+      <c r="AF51" s="19" t="inlineStr">
+        <is>
+          <t>廃店フラグ（true:廃店, false:営業中）</t>
+        </is>
+      </c>
+      <c r="AG51" s="10" t="n"/>
+      <c r="AH51" s="10" t="n"/>
+      <c r="AI51" s="10" t="n"/>
+      <c r="AJ51" s="10" t="n"/>
+      <c r="AK51" s="11" t="n"/>
+    </row>
+    <row r="52" ht="19.5" customHeight="1"/>
+    <row r="53" ht="19.5" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="19.5" customHeight="1"/>
-    <row r="54" ht="19.5" customHeight="1">
-      <c r="B54" s="30" t="inlineStr">
+    <row r="54" ht="19.5" customHeight="1"/>
+    <row r="55" ht="19.5" customHeight="1">
+      <c r="B55" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C54" s="16" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="10" t="n"/>
-      <c r="G54" s="10" t="n"/>
-      <c r="H54" s="10" t="n"/>
-      <c r="I54" s="10" t="n"/>
-      <c r="J54" s="10" t="n"/>
-      <c r="K54" s="10" t="n"/>
-      <c r="L54" s="11" t="n"/>
-      <c r="M54" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N54" s="10" t="n"/>
-      <c r="O54" s="10" t="n"/>
-      <c r="P54" s="11" t="n"/>
-      <c r="Q54" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R54" s="10" t="n"/>
-      <c r="S54" s="11" t="n"/>
-      <c r="T54" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U54" s="10" t="n"/>
-      <c r="V54" s="10" t="n"/>
-      <c r="W54" s="10" t="n"/>
-      <c r="X54" s="11" t="n"/>
-      <c r="Y54" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z54" s="10" t="n"/>
-      <c r="AA54" s="10" t="n"/>
-      <c r="AB54" s="10" t="n"/>
-      <c r="AC54" s="10" t="n"/>
-      <c r="AD54" s="10" t="n"/>
-      <c r="AE54" s="11" t="n"/>
-      <c r="AF54" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG54" s="10" t="n"/>
-      <c r="AH54" s="10" t="n"/>
-      <c r="AI54" s="10" t="n"/>
-      <c r="AJ54" s="10" t="n"/>
-      <c r="AK54" s="11" t="n"/>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="B55" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
         </is>
       </c>
       <c r="D55" s="10" t="n"/>
@@ -9249,29 +9223,33 @@
       <c r="J55" s="10" t="n"/>
       <c r="K55" s="10" t="n"/>
       <c r="L55" s="11" t="n"/>
-      <c r="M55" s="17" t="inlineStr">
-        <is>
-          <t>Object</t>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N55" s="10" t="n"/>
       <c r="O55" s="10" t="n"/>
       <c r="P55" s="11" t="n"/>
-      <c r="Q55" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q55" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R55" s="10" t="n"/>
       <c r="S55" s="11" t="n"/>
-      <c r="T55" s="17" t="inlineStr"/>
+      <c r="T55" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
       <c r="W55" s="10" t="n"/>
       <c r="X55" s="11" t="n"/>
-      <c r="Y55" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y55" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z55" s="10" t="n"/>
@@ -9280,9 +9258,9 @@
       <c r="AC55" s="10" t="n"/>
       <c r="AD55" s="10" t="n"/>
       <c r="AE55" s="11" t="n"/>
-      <c r="AF55" s="19" t="inlineStr">
-        <is>
-          <t>取込結果サマリ</t>
+      <c r="AF55" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG55" s="10" t="n"/>
@@ -9293,14 +9271,14 @@
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C56" s="39" t="n"/>
-      <c r="D56" s="19" t="inlineStr">
-        <is>
-          <t>import_mode</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n"/>
       <c r="E56" s="10" t="n"/>
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
@@ -9311,7 +9289,7 @@
       <c r="L56" s="11" t="n"/>
       <c r="M56" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N56" s="10" t="n"/>
@@ -9342,7 +9320,7 @@
       <c r="AE56" s="11" t="n"/>
       <c r="AF56" s="19" t="inlineStr">
         <is>
-          <t>実行した取込モード</t>
+          <t>取込結果サマリ</t>
         </is>
       </c>
       <c r="AG56" s="10" t="n"/>
@@ -9353,12 +9331,12 @@
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C57" s="40" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C57" s="39" t="n"/>
       <c r="D57" s="19" t="inlineStr">
         <is>
-          <t>total_rows</t>
+          <t>import_mode</t>
         </is>
       </c>
       <c r="E57" s="10" t="n"/>
@@ -9371,7 +9349,7 @@
       <c r="L57" s="11" t="n"/>
       <c r="M57" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N57" s="10" t="n"/>
@@ -9402,7 +9380,7 @@
       <c r="AE57" s="11" t="n"/>
       <c r="AF57" s="19" t="inlineStr">
         <is>
-          <t>取込対象行数</t>
+          <t>実行した取込モード</t>
         </is>
       </c>
       <c r="AG57" s="10" t="n"/>
@@ -9413,12 +9391,12 @@
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C58" s="40" t="n"/>
       <c r="D58" s="19" t="inlineStr">
         <is>
-          <t>created_count</t>
+          <t>total_rows</t>
         </is>
       </c>
       <c r="E58" s="10" t="n"/>
@@ -9462,7 +9440,7 @@
       <c r="AE58" s="11" t="n"/>
       <c r="AF58" s="19" t="inlineStr">
         <is>
-          <t>新規登録件数</t>
+          <t>取込対象行数</t>
         </is>
       </c>
       <c r="AG58" s="10" t="n"/>
@@ -9473,12 +9451,12 @@
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C59" s="40" t="n"/>
       <c r="D59" s="19" t="inlineStr">
         <is>
-          <t>updated_count</t>
+          <t>created_count</t>
         </is>
       </c>
       <c r="E59" s="10" t="n"/>
@@ -9522,7 +9500,7 @@
       <c r="AE59" s="11" t="n"/>
       <c r="AF59" s="19" t="inlineStr">
         <is>
-          <t>更新件数</t>
+          <t>新規登録件数</t>
         </is>
       </c>
       <c r="AG59" s="10" t="n"/>
@@ -9533,12 +9511,12 @@
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60" s="40" t="n"/>
       <c r="D60" s="19" t="inlineStr">
         <is>
-          <t>skipped_count</t>
+          <t>updated_count</t>
         </is>
       </c>
       <c r="E60" s="10" t="n"/>
@@ -9582,7 +9560,7 @@
       <c r="AE60" s="11" t="n"/>
       <c r="AF60" s="19" t="inlineStr">
         <is>
-          <t>スキップ件数</t>
+          <t>更新件数</t>
         </is>
       </c>
       <c r="AG60" s="10" t="n"/>
@@ -9593,12 +9571,12 @@
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="C61" s="41" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="C61" s="40" t="n"/>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>imported_at</t>
+          <t>skipped_count</t>
         </is>
       </c>
       <c r="E61" s="10" t="n"/>
@@ -9611,7 +9589,7 @@
       <c r="L61" s="11" t="n"/>
       <c r="M61" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N61" s="10" t="n"/>
@@ -9624,11 +9602,7 @@
       </c>
       <c r="R61" s="10" t="n"/>
       <c r="S61" s="11" t="n"/>
-      <c r="T61" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T61" s="17" t="inlineStr"/>
       <c r="U61" s="10" t="n"/>
       <c r="V61" s="10" t="n"/>
       <c r="W61" s="10" t="n"/>
@@ -9646,7 +9620,7 @@
       <c r="AE61" s="11" t="n"/>
       <c r="AF61" s="19" t="inlineStr">
         <is>
-          <t>取込完了日時</t>
+          <t>スキップ件数</t>
         </is>
       </c>
       <c r="AG61" s="10" t="n"/>
@@ -9657,14 +9631,14 @@
     </row>
     <row r="62" ht="18" customHeight="1">
       <c r="B62" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="C62" s="19" t="inlineStr">
-        <is>
-          <t>message</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="C62" s="41" t="n"/>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>imported_at</t>
+        </is>
+      </c>
       <c r="E62" s="10" t="n"/>
       <c r="F62" s="10" t="n"/>
       <c r="G62" s="10" t="n"/>
@@ -9688,7 +9662,11 @@
       </c>
       <c r="R62" s="10" t="n"/>
       <c r="S62" s="11" t="n"/>
-      <c r="T62" s="17" t="inlineStr"/>
+      <c r="T62" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U62" s="10" t="n"/>
       <c r="V62" s="10" t="n"/>
       <c r="W62" s="10" t="n"/>
@@ -9706,7 +9684,7 @@
       <c r="AE62" s="11" t="n"/>
       <c r="AF62" s="19" t="inlineStr">
         <is>
-          <t>正常に取り込みました。</t>
+          <t>取込完了日時</t>
         </is>
       </c>
       <c r="AG62" s="10" t="n"/>
@@ -9715,16 +9693,76 @@
       <c r="AJ62" s="10" t="n"/>
       <c r="AK62" s="11" t="n"/>
     </row>
-    <row r="63" ht="19.5" customHeight="1"/>
-    <row r="64" ht="19.5" customHeight="1">
-      <c r="B64" s="37" t="inlineStr">
+    <row r="63" ht="18" customHeight="1">
+      <c r="B63" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="11" t="n"/>
+      <c r="M63" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="11" t="n"/>
+      <c r="T63" s="17" t="inlineStr"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="10" t="n"/>
+      <c r="X63" s="11" t="n"/>
+      <c r="Y63" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="10" t="n"/>
+      <c r="AE63" s="11" t="n"/>
+      <c r="AF63" s="19" t="inlineStr">
+        <is>
+          <t>取り込みました。</t>
+        </is>
+      </c>
+      <c r="AG63" s="10" t="n"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="10" t="n"/>
+      <c r="AJ63" s="10" t="n"/>
+      <c r="AK63" s="11" t="n"/>
+    </row>
+    <row r="64" ht="19.5" customHeight="1"/>
+    <row r="65" ht="19.5" customHeight="1">
+      <c r="B65" s="37" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="409" customHeight="1">
-      <c r="C65" s="19" t="inlineStr">
+    <row r="66" ht="409" customHeight="1">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>POST /api/v1/hanbaiten/import
 Content-Type: application/json
@@ -9768,50 +9806,50 @@
 }</t>
         </is>
       </c>
-      <c r="D65" s="10" t="n"/>
-      <c r="E65" s="10" t="n"/>
-      <c r="F65" s="10" t="n"/>
-      <c r="G65" s="10" t="n"/>
-      <c r="H65" s="10" t="n"/>
-      <c r="I65" s="10" t="n"/>
-      <c r="J65" s="10" t="n"/>
-      <c r="K65" s="10" t="n"/>
-      <c r="L65" s="10" t="n"/>
-      <c r="M65" s="10" t="n"/>
-      <c r="N65" s="10" t="n"/>
-      <c r="O65" s="10" t="n"/>
-      <c r="P65" s="10" t="n"/>
-      <c r="Q65" s="10" t="n"/>
-      <c r="R65" s="10" t="n"/>
-      <c r="S65" s="10" t="n"/>
-      <c r="T65" s="10" t="n"/>
-      <c r="U65" s="10" t="n"/>
-      <c r="V65" s="10" t="n"/>
-      <c r="W65" s="10" t="n"/>
-      <c r="X65" s="10" t="n"/>
-      <c r="Y65" s="10" t="n"/>
-      <c r="Z65" s="10" t="n"/>
-      <c r="AA65" s="10" t="n"/>
-      <c r="AB65" s="10" t="n"/>
-      <c r="AC65" s="10" t="n"/>
-      <c r="AD65" s="10" t="n"/>
-      <c r="AE65" s="10" t="n"/>
-      <c r="AF65" s="10" t="n"/>
-      <c r="AG65" s="10" t="n"/>
-      <c r="AH65" s="10" t="n"/>
-      <c r="AI65" s="10" t="n"/>
-      <c r="AJ65" s="10" t="n"/>
-      <c r="AK65" s="11" t="n"/>
-    </row>
-    <row r="67" ht="19.5" customHeight="1">
-      <c r="B67" s="37" t="inlineStr">
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="10" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n"/>
+      <c r="J66" s="10" t="n"/>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="10" t="n"/>
+      <c r="X66" s="10" t="n"/>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="10" t="n"/>
+      <c r="AE66" s="10" t="n"/>
+      <c r="AF66" s="10" t="n"/>
+      <c r="AG66" s="10" t="n"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="10" t="n"/>
+      <c r="AJ66" s="10" t="n"/>
+      <c r="AK66" s="11" t="n"/>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="B68" s="37" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="198" customHeight="1">
-      <c r="C68" s="19" t="inlineStr">
+    <row r="69" ht="198" customHeight="1">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>{
   "data": {
@@ -9822,54 +9860,54 @@
     "skipped_count": 0,
     "imported_at": "2026-04-22T10:00:00Z"
   },
-  "message": "正常に取り込みました。"
+  "message": "取り込みました。"
 }</t>
         </is>
       </c>
-      <c r="D68" s="10" t="n"/>
-      <c r="E68" s="10" t="n"/>
-      <c r="F68" s="10" t="n"/>
-      <c r="G68" s="10" t="n"/>
-      <c r="H68" s="10" t="n"/>
-      <c r="I68" s="10" t="n"/>
-      <c r="J68" s="10" t="n"/>
-      <c r="K68" s="10" t="n"/>
-      <c r="L68" s="10" t="n"/>
-      <c r="M68" s="10" t="n"/>
-      <c r="N68" s="10" t="n"/>
-      <c r="O68" s="10" t="n"/>
-      <c r="P68" s="10" t="n"/>
-      <c r="Q68" s="10" t="n"/>
-      <c r="R68" s="10" t="n"/>
-      <c r="S68" s="10" t="n"/>
-      <c r="T68" s="10" t="n"/>
-      <c r="U68" s="10" t="n"/>
-      <c r="V68" s="10" t="n"/>
-      <c r="W68" s="10" t="n"/>
-      <c r="X68" s="10" t="n"/>
-      <c r="Y68" s="10" t="n"/>
-      <c r="Z68" s="10" t="n"/>
-      <c r="AA68" s="10" t="n"/>
-      <c r="AB68" s="10" t="n"/>
-      <c r="AC68" s="10" t="n"/>
-      <c r="AD68" s="10" t="n"/>
-      <c r="AE68" s="10" t="n"/>
-      <c r="AF68" s="10" t="n"/>
-      <c r="AG68" s="10" t="n"/>
-      <c r="AH68" s="10" t="n"/>
-      <c r="AI68" s="10" t="n"/>
-      <c r="AJ68" s="10" t="n"/>
-      <c r="AK68" s="11" t="n"/>
-    </row>
-    <row r="70" ht="19.5" customHeight="1">
-      <c r="B70" s="37" t="inlineStr">
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="10" t="n"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="10" t="n"/>
+      <c r="X69" s="10" t="n"/>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="10" t="n"/>
+      <c r="AE69" s="10" t="n"/>
+      <c r="AF69" s="10" t="n"/>
+      <c r="AG69" s="10" t="n"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="10" t="n"/>
+      <c r="AJ69" s="10" t="n"/>
+      <c r="AK69" s="11" t="n"/>
+    </row>
+    <row r="71" ht="19.5" customHeight="1">
+      <c r="B71" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Validation Error)）</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="144" customHeight="1">
-      <c r="C71" s="19" t="inlineStr">
+    <row r="72" ht="144" customHeight="1">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "VALIDATION_ERROR",
@@ -9881,50 +9919,50 @@
 }</t>
         </is>
       </c>
-      <c r="D71" s="10" t="n"/>
-      <c r="E71" s="10" t="n"/>
-      <c r="F71" s="10" t="n"/>
-      <c r="G71" s="10" t="n"/>
-      <c r="H71" s="10" t="n"/>
-      <c r="I71" s="10" t="n"/>
-      <c r="J71" s="10" t="n"/>
-      <c r="K71" s="10" t="n"/>
-      <c r="L71" s="10" t="n"/>
-      <c r="M71" s="10" t="n"/>
-      <c r="N71" s="10" t="n"/>
-      <c r="O71" s="10" t="n"/>
-      <c r="P71" s="10" t="n"/>
-      <c r="Q71" s="10" t="n"/>
-      <c r="R71" s="10" t="n"/>
-      <c r="S71" s="10" t="n"/>
-      <c r="T71" s="10" t="n"/>
-      <c r="U71" s="10" t="n"/>
-      <c r="V71" s="10" t="n"/>
-      <c r="W71" s="10" t="n"/>
-      <c r="X71" s="10" t="n"/>
-      <c r="Y71" s="10" t="n"/>
-      <c r="Z71" s="10" t="n"/>
-      <c r="AA71" s="10" t="n"/>
-      <c r="AB71" s="10" t="n"/>
-      <c r="AC71" s="10" t="n"/>
-      <c r="AD71" s="10" t="n"/>
-      <c r="AE71" s="10" t="n"/>
-      <c r="AF71" s="10" t="n"/>
-      <c r="AG71" s="10" t="n"/>
-      <c r="AH71" s="10" t="n"/>
-      <c r="AI71" s="10" t="n"/>
-      <c r="AJ71" s="10" t="n"/>
-      <c r="AK71" s="11" t="n"/>
-    </row>
-    <row r="73" ht="19.5" customHeight="1">
-      <c r="B73" s="37" t="inlineStr">
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="10" t="n"/>
+      <c r="X72" s="10" t="n"/>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="10" t="n"/>
+      <c r="AE72" s="10" t="n"/>
+      <c r="AF72" s="10" t="n"/>
+      <c r="AG72" s="10" t="n"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="10" t="n"/>
+      <c r="AJ72" s="10" t="n"/>
+      <c r="AK72" s="11" t="n"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="B74" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Import Validation Error — 行別エラー)）</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="180" customHeight="1">
-      <c r="C74" s="19" t="inlineStr">
+    <row r="75" ht="180" customHeight="1">
+      <c r="C75" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "IMPORT_VALIDATION_ERROR",
@@ -9933,55 +9971,55 @@
     { "row": 2, "field": "hanbaiten_code", "message": "販売店コードは必須です" },
     { "row": 3, "field": "hanbaiten_code", "message": "同一の販売店コードが既に登録されています" },
     { "row": 5, "field": "haitatsuryo_tanka_code", "message": "指定された配達手数料単価コードが見つかりません" },
-    { "row": 7, "field": "itaku_kubun", "message": "委託区分は 1, 2, 9 のいずれかを指定してください" }
+    { "row": 7, "field": "itaku_kubun", "message": "委託区分の値が不正です" }
   ]
 }</t>
         </is>
       </c>
-      <c r="D74" s="10" t="n"/>
-      <c r="E74" s="10" t="n"/>
-      <c r="F74" s="10" t="n"/>
-      <c r="G74" s="10" t="n"/>
-      <c r="H74" s="10" t="n"/>
-      <c r="I74" s="10" t="n"/>
-      <c r="J74" s="10" t="n"/>
-      <c r="K74" s="10" t="n"/>
-      <c r="L74" s="10" t="n"/>
-      <c r="M74" s="10" t="n"/>
-      <c r="N74" s="10" t="n"/>
-      <c r="O74" s="10" t="n"/>
-      <c r="P74" s="10" t="n"/>
-      <c r="Q74" s="10" t="n"/>
-      <c r="R74" s="10" t="n"/>
-      <c r="S74" s="10" t="n"/>
-      <c r="T74" s="10" t="n"/>
-      <c r="U74" s="10" t="n"/>
-      <c r="V74" s="10" t="n"/>
-      <c r="W74" s="10" t="n"/>
-      <c r="X74" s="10" t="n"/>
-      <c r="Y74" s="10" t="n"/>
-      <c r="Z74" s="10" t="n"/>
-      <c r="AA74" s="10" t="n"/>
-      <c r="AB74" s="10" t="n"/>
-      <c r="AC74" s="10" t="n"/>
-      <c r="AD74" s="10" t="n"/>
-      <c r="AE74" s="10" t="n"/>
-      <c r="AF74" s="10" t="n"/>
-      <c r="AG74" s="10" t="n"/>
-      <c r="AH74" s="10" t="n"/>
-      <c r="AI74" s="10" t="n"/>
-      <c r="AJ74" s="10" t="n"/>
-      <c r="AK74" s="11" t="n"/>
-    </row>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="B76" s="37" t="inlineStr">
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="10" t="n"/>
+      <c r="J75" s="10" t="n"/>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="10" t="n"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="10" t="n"/>
+      <c r="X75" s="10" t="n"/>
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="10" t="n"/>
+      <c r="AD75" s="10" t="n"/>
+      <c r="AE75" s="10" t="n"/>
+      <c r="AF75" s="10" t="n"/>
+      <c r="AG75" s="10" t="n"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="10" t="n"/>
+      <c r="AJ75" s="10" t="n"/>
+      <c r="AK75" s="11" t="n"/>
+    </row>
+    <row r="77" ht="19.5" customHeight="1">
+      <c r="B77" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 400 Bad Request (Row Limit Exceeded)）</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="72" customHeight="1">
-      <c r="C77" s="19" t="inlineStr">
+    <row r="78" ht="72" customHeight="1">
+      <c r="C78" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "ROW_LIMIT_EXCEEDED",
@@ -9989,50 +10027,50 @@
 }</t>
         </is>
       </c>
-      <c r="D77" s="10" t="n"/>
-      <c r="E77" s="10" t="n"/>
-      <c r="F77" s="10" t="n"/>
-      <c r="G77" s="10" t="n"/>
-      <c r="H77" s="10" t="n"/>
-      <c r="I77" s="10" t="n"/>
-      <c r="J77" s="10" t="n"/>
-      <c r="K77" s="10" t="n"/>
-      <c r="L77" s="10" t="n"/>
-      <c r="M77" s="10" t="n"/>
-      <c r="N77" s="10" t="n"/>
-      <c r="O77" s="10" t="n"/>
-      <c r="P77" s="10" t="n"/>
-      <c r="Q77" s="10" t="n"/>
-      <c r="R77" s="10" t="n"/>
-      <c r="S77" s="10" t="n"/>
-      <c r="T77" s="10" t="n"/>
-      <c r="U77" s="10" t="n"/>
-      <c r="V77" s="10" t="n"/>
-      <c r="W77" s="10" t="n"/>
-      <c r="X77" s="10" t="n"/>
-      <c r="Y77" s="10" t="n"/>
-      <c r="Z77" s="10" t="n"/>
-      <c r="AA77" s="10" t="n"/>
-      <c r="AB77" s="10" t="n"/>
-      <c r="AC77" s="10" t="n"/>
-      <c r="AD77" s="10" t="n"/>
-      <c r="AE77" s="10" t="n"/>
-      <c r="AF77" s="10" t="n"/>
-      <c r="AG77" s="10" t="n"/>
-      <c r="AH77" s="10" t="n"/>
-      <c r="AI77" s="10" t="n"/>
-      <c r="AJ77" s="10" t="n"/>
-      <c r="AK77" s="11" t="n"/>
-    </row>
-    <row r="79" ht="19.5" customHeight="1">
-      <c r="B79" s="37" t="inlineStr">
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="n"/>
+      <c r="J78" s="10" t="n"/>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="10" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="10" t="n"/>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="10" t="n"/>
+      <c r="X78" s="10" t="n"/>
+      <c r="Y78" s="10" t="n"/>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="10" t="n"/>
+      <c r="AD78" s="10" t="n"/>
+      <c r="AE78" s="10" t="n"/>
+      <c r="AF78" s="10" t="n"/>
+      <c r="AG78" s="10" t="n"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="10" t="n"/>
+      <c r="AJ78" s="10" t="n"/>
+      <c r="AK78" s="11" t="n"/>
+    </row>
+    <row r="80" ht="19.5" customHeight="1">
+      <c r="B80" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="72" customHeight="1">
-      <c r="C80" s="19" t="inlineStr">
+    <row r="81" ht="72" customHeight="1">
+      <c r="C81" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -10040,50 +10078,50 @@
 }</t>
         </is>
       </c>
-      <c r="D80" s="10" t="n"/>
-      <c r="E80" s="10" t="n"/>
-      <c r="F80" s="10" t="n"/>
-      <c r="G80" s="10" t="n"/>
-      <c r="H80" s="10" t="n"/>
-      <c r="I80" s="10" t="n"/>
-      <c r="J80" s="10" t="n"/>
-      <c r="K80" s="10" t="n"/>
-      <c r="L80" s="10" t="n"/>
-      <c r="M80" s="10" t="n"/>
-      <c r="N80" s="10" t="n"/>
-      <c r="O80" s="10" t="n"/>
-      <c r="P80" s="10" t="n"/>
-      <c r="Q80" s="10" t="n"/>
-      <c r="R80" s="10" t="n"/>
-      <c r="S80" s="10" t="n"/>
-      <c r="T80" s="10" t="n"/>
-      <c r="U80" s="10" t="n"/>
-      <c r="V80" s="10" t="n"/>
-      <c r="W80" s="10" t="n"/>
-      <c r="X80" s="10" t="n"/>
-      <c r="Y80" s="10" t="n"/>
-      <c r="Z80" s="10" t="n"/>
-      <c r="AA80" s="10" t="n"/>
-      <c r="AB80" s="10" t="n"/>
-      <c r="AC80" s="10" t="n"/>
-      <c r="AD80" s="10" t="n"/>
-      <c r="AE80" s="10" t="n"/>
-      <c r="AF80" s="10" t="n"/>
-      <c r="AG80" s="10" t="n"/>
-      <c r="AH80" s="10" t="n"/>
-      <c r="AI80" s="10" t="n"/>
-      <c r="AJ80" s="10" t="n"/>
-      <c r="AK80" s="11" t="n"/>
-    </row>
-    <row r="82" ht="19.5" customHeight="1">
-      <c r="B82" s="37" t="inlineStr">
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
+      <c r="U81" s="10" t="n"/>
+      <c r="V81" s="10" t="n"/>
+      <c r="W81" s="10" t="n"/>
+      <c r="X81" s="10" t="n"/>
+      <c r="Y81" s="10" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
+      <c r="AB81" s="10" t="n"/>
+      <c r="AC81" s="10" t="n"/>
+      <c r="AD81" s="10" t="n"/>
+      <c r="AE81" s="10" t="n"/>
+      <c r="AF81" s="10" t="n"/>
+      <c r="AG81" s="10" t="n"/>
+      <c r="AH81" s="10" t="n"/>
+      <c r="AI81" s="10" t="n"/>
+      <c r="AJ81" s="10" t="n"/>
+      <c r="AK81" s="11" t="n"/>
+    </row>
+    <row r="83" ht="19.5" customHeight="1">
+      <c r="B83" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="72" customHeight="1">
-      <c r="C83" s="19" t="inlineStr">
+    <row r="84" ht="72" customHeight="1">
+      <c r="C84" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -10091,50 +10129,50 @@
 }</t>
         </is>
       </c>
-      <c r="D83" s="10" t="n"/>
-      <c r="E83" s="10" t="n"/>
-      <c r="F83" s="10" t="n"/>
-      <c r="G83" s="10" t="n"/>
-      <c r="H83" s="10" t="n"/>
-      <c r="I83" s="10" t="n"/>
-      <c r="J83" s="10" t="n"/>
-      <c r="K83" s="10" t="n"/>
-      <c r="L83" s="10" t="n"/>
-      <c r="M83" s="10" t="n"/>
-      <c r="N83" s="10" t="n"/>
-      <c r="O83" s="10" t="n"/>
-      <c r="P83" s="10" t="n"/>
-      <c r="Q83" s="10" t="n"/>
-      <c r="R83" s="10" t="n"/>
-      <c r="S83" s="10" t="n"/>
-      <c r="T83" s="10" t="n"/>
-      <c r="U83" s="10" t="n"/>
-      <c r="V83" s="10" t="n"/>
-      <c r="W83" s="10" t="n"/>
-      <c r="X83" s="10" t="n"/>
-      <c r="Y83" s="10" t="n"/>
-      <c r="Z83" s="10" t="n"/>
-      <c r="AA83" s="10" t="n"/>
-      <c r="AB83" s="10" t="n"/>
-      <c r="AC83" s="10" t="n"/>
-      <c r="AD83" s="10" t="n"/>
-      <c r="AE83" s="10" t="n"/>
-      <c r="AF83" s="10" t="n"/>
-      <c r="AG83" s="10" t="n"/>
-      <c r="AH83" s="10" t="n"/>
-      <c r="AI83" s="10" t="n"/>
-      <c r="AJ83" s="10" t="n"/>
-      <c r="AK83" s="11" t="n"/>
-    </row>
-    <row r="85" ht="19.5" customHeight="1">
-      <c r="B85" s="37" t="inlineStr">
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="10" t="n"/>
+      <c r="J84" s="10" t="n"/>
+      <c r="K84" s="10" t="n"/>
+      <c r="L84" s="10" t="n"/>
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="10" t="n"/>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="10" t="n"/>
+      <c r="T84" s="10" t="n"/>
+      <c r="U84" s="10" t="n"/>
+      <c r="V84" s="10" t="n"/>
+      <c r="W84" s="10" t="n"/>
+      <c r="X84" s="10" t="n"/>
+      <c r="Y84" s="10" t="n"/>
+      <c r="Z84" s="10" t="n"/>
+      <c r="AA84" s="10" t="n"/>
+      <c r="AB84" s="10" t="n"/>
+      <c r="AC84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="10" t="n"/>
+      <c r="AF84" s="10" t="n"/>
+      <c r="AG84" s="10" t="n"/>
+      <c r="AH84" s="10" t="n"/>
+      <c r="AI84" s="10" t="n"/>
+      <c r="AJ84" s="10" t="n"/>
+      <c r="AK84" s="11" t="n"/>
+    </row>
+    <row r="86" ht="19.5" customHeight="1">
+      <c r="B86" s="37" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="72" customHeight="1">
-      <c r="C86" s="19" t="inlineStr">
+    <row r="87" ht="72" customHeight="1">
+      <c r="C87" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -10142,228 +10180,235 @@
 }</t>
         </is>
       </c>
-      <c r="D86" s="10" t="n"/>
-      <c r="E86" s="10" t="n"/>
-      <c r="F86" s="10" t="n"/>
-      <c r="G86" s="10" t="n"/>
-      <c r="H86" s="10" t="n"/>
-      <c r="I86" s="10" t="n"/>
-      <c r="J86" s="10" t="n"/>
-      <c r="K86" s="10" t="n"/>
-      <c r="L86" s="10" t="n"/>
-      <c r="M86" s="10" t="n"/>
-      <c r="N86" s="10" t="n"/>
-      <c r="O86" s="10" t="n"/>
-      <c r="P86" s="10" t="n"/>
-      <c r="Q86" s="10" t="n"/>
-      <c r="R86" s="10" t="n"/>
-      <c r="S86" s="10" t="n"/>
-      <c r="T86" s="10" t="n"/>
-      <c r="U86" s="10" t="n"/>
-      <c r="V86" s="10" t="n"/>
-      <c r="W86" s="10" t="n"/>
-      <c r="X86" s="10" t="n"/>
-      <c r="Y86" s="10" t="n"/>
-      <c r="Z86" s="10" t="n"/>
-      <c r="AA86" s="10" t="n"/>
-      <c r="AB86" s="10" t="n"/>
-      <c r="AC86" s="10" t="n"/>
-      <c r="AD86" s="10" t="n"/>
-      <c r="AE86" s="10" t="n"/>
-      <c r="AF86" s="10" t="n"/>
-      <c r="AG86" s="10" t="n"/>
-      <c r="AH86" s="10" t="n"/>
-      <c r="AI86" s="10" t="n"/>
-      <c r="AJ86" s="10" t="n"/>
-      <c r="AK86" s="11" t="n"/>
-    </row>
-    <row r="88" ht="19.5" customHeight="1"/>
-    <row r="89" ht="19.5" customHeight="1">
-      <c r="A89" s="27" t="inlineStr">
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="10" t="n"/>
+      <c r="K87" s="10" t="n"/>
+      <c r="L87" s="10" t="n"/>
+      <c r="M87" s="10" t="n"/>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="10" t="n"/>
+      <c r="S87" s="10" t="n"/>
+      <c r="T87" s="10" t="n"/>
+      <c r="U87" s="10" t="n"/>
+      <c r="V87" s="10" t="n"/>
+      <c r="W87" s="10" t="n"/>
+      <c r="X87" s="10" t="n"/>
+      <c r="Y87" s="10" t="n"/>
+      <c r="Z87" s="10" t="n"/>
+      <c r="AA87" s="10" t="n"/>
+      <c r="AB87" s="10" t="n"/>
+      <c r="AC87" s="10" t="n"/>
+      <c r="AD87" s="10" t="n"/>
+      <c r="AE87" s="10" t="n"/>
+      <c r="AF87" s="10" t="n"/>
+      <c r="AG87" s="10" t="n"/>
+      <c r="AH87" s="10" t="n"/>
+      <c r="AI87" s="10" t="n"/>
+      <c r="AJ87" s="10" t="n"/>
+      <c r="AK87" s="11" t="n"/>
+    </row>
+    <row r="89" ht="19.5" customHeight="1"/>
+    <row r="90" ht="19.5" customHeight="1">
+      <c r="A90" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="54" customHeight="1">
-      <c r="B90" s="42" t="inlineStr">
+    <row r="91" ht="54" customHeight="1">
+      <c r="B91" s="42" t="inlineStr">
         <is>
           <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
 いずれかが失敗した場合は全てロールバックすること。
 例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
         </is>
       </c>
-      <c r="C90" s="10" t="n"/>
-      <c r="D90" s="10" t="n"/>
-      <c r="E90" s="10" t="n"/>
-      <c r="F90" s="10" t="n"/>
-      <c r="G90" s="10" t="n"/>
-      <c r="H90" s="10" t="n"/>
-      <c r="I90" s="10" t="n"/>
-      <c r="J90" s="10" t="n"/>
-      <c r="K90" s="10" t="n"/>
-      <c r="L90" s="10" t="n"/>
-      <c r="M90" s="10" t="n"/>
-      <c r="N90" s="10" t="n"/>
-      <c r="O90" s="10" t="n"/>
-      <c r="P90" s="10" t="n"/>
-      <c r="Q90" s="10" t="n"/>
-      <c r="R90" s="10" t="n"/>
-      <c r="S90" s="10" t="n"/>
-      <c r="T90" s="10" t="n"/>
-      <c r="U90" s="10" t="n"/>
-      <c r="V90" s="10" t="n"/>
-      <c r="W90" s="10" t="n"/>
-      <c r="X90" s="10" t="n"/>
-      <c r="Y90" s="10" t="n"/>
-      <c r="Z90" s="10" t="n"/>
-      <c r="AA90" s="10" t="n"/>
-      <c r="AB90" s="10" t="n"/>
-      <c r="AC90" s="10" t="n"/>
-      <c r="AD90" s="10" t="n"/>
-      <c r="AE90" s="10" t="n"/>
-      <c r="AF90" s="10" t="n"/>
-      <c r="AG90" s="10" t="n"/>
-      <c r="AH90" s="10" t="n"/>
-      <c r="AI90" s="10" t="n"/>
-      <c r="AJ90" s="10" t="n"/>
-      <c r="AK90" s="11" t="n"/>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="B91" s="27" t="inlineStr">
+      <c r="C91" s="10" t="n"/>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="10" t="n"/>
+      <c r="J91" s="10" t="n"/>
+      <c r="K91" s="10" t="n"/>
+      <c r="L91" s="10" t="n"/>
+      <c r="M91" s="10" t="n"/>
+      <c r="N91" s="10" t="n"/>
+      <c r="O91" s="10" t="n"/>
+      <c r="P91" s="10" t="n"/>
+      <c r="Q91" s="10" t="n"/>
+      <c r="R91" s="10" t="n"/>
+      <c r="S91" s="10" t="n"/>
+      <c r="T91" s="10" t="n"/>
+      <c r="U91" s="10" t="n"/>
+      <c r="V91" s="10" t="n"/>
+      <c r="W91" s="10" t="n"/>
+      <c r="X91" s="10" t="n"/>
+      <c r="Y91" s="10" t="n"/>
+      <c r="Z91" s="10" t="n"/>
+      <c r="AA91" s="10" t="n"/>
+      <c r="AB91" s="10" t="n"/>
+      <c r="AC91" s="10" t="n"/>
+      <c r="AD91" s="10" t="n"/>
+      <c r="AE91" s="10" t="n"/>
+      <c r="AF91" s="10" t="n"/>
+      <c r="AG91" s="10" t="n"/>
+      <c r="AH91" s="10" t="n"/>
+      <c r="AI91" s="10" t="n"/>
+      <c r="AJ91" s="10" t="n"/>
+      <c r="AK91" s="11" t="n"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="B92" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="C92" s="38" t="inlineStr">
+    <row r="93" ht="18" customHeight="1">
+      <c r="C93" s="38" t="inlineStr">
         <is>
           <t>リクエストボディの検証：</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="36" customHeight="1">
-      <c r="D93" s="38" t="inlineStr">
-        <is>
-          <t>import_mode：必須、`NEW` / `UPDATE_ALL` / `UPDATE_PARTIAL` のいずれか</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="36" customHeight="1">
+    <row r="94" ht="54" customHeight="1">
       <c r="D94" s="38" t="inlineStr">
         <is>
-          <t>selected_columns：必須、配列、1件以上、`hanbaiten_code` を必ず含むこと</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
+          <t>import_mode：必須、`NEW` / `UPDATE` のいずれか（2026-07 顧客要件により旧 `UPDATE_ALL` / `UPDATE_PARTIAL` は `UPDATE` に統合済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="54" customHeight="1">
       <c r="D95" s="38" t="inlineStr">
         <is>
-          <t>rows：必須、配列、1件以上、500件以下</t>
+          <t>selected_columns：必須、配列、1件以上23件以下。`UPDATE` モードは `hanbaiten_code` を必ず含むこと（含まれない場合：HTTP 400 `VALIDATION_ERROR`、field='selected_columns'）</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="D96" s="38" t="inlineStr">
         <is>
+          <t>rows：必須、配列、1件以上、500件以下</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="D97" s="38" t="inlineStr">
+        <is>
           <t>各行 rows[i] の検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="36" customHeight="1">
-      <c r="C97" s="38" t="inlineStr">
-        <is>
-          <t>トップレベルのバリデーションエラー：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
         </is>
       </c>
     </row>
     <row r="98" ht="36" customHeight="1">
       <c r="C98" s="38" t="inlineStr">
         <is>
+          <t>トップレベルのバリデーションエラー：HTTP 400 (`VALIDATION_ERROR`) + errors配列</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
+      <c r="C99" s="38" t="inlineStr">
+        <is>
           <t>行レベルのバリデーションエラー：HTTP 400 (`IMPORT_VALIDATION_ERROR`) + errors配列（row番号含む）</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="B99" s="27" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="B100" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="C100" s="38" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
       <c r="C101" s="38" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="C102" s="38" t="inlineStr">
         <is>
+          <t>認証失敗の場合：HTTP 401 (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="C103" s="38" t="inlineStr">
+        <is>
           <t>権限チェック：`hanbaiten.import` を保持しているか確認する。</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="36" customHeight="1">
-      <c r="D103" s="38" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="C104" s="38" t="inlineStr">
+    <row r="104" ht="36" customHeight="1">
+      <c r="D104" s="38" t="inlineStr">
+        <is>
+          <t>対象ロール：CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="C105" s="38" t="inlineStr">
         <is>
           <t>権限がない場合：HTTP 403 (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="36" customHeight="1">
-      <c r="C105" s="38" t="inlineStr">
+    <row r="106" ht="36" customHeight="1">
+      <c r="C106" s="38" t="inlineStr">
         <is>
           <t>DataScope：ログインユーザーの `ja_id` を取得する。全行は当該 `ja_id` のデータとして扱う。</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="B106" s="27" t="inlineStr">
+    <row r="107" ht="72" customHeight="1">
+      <c r="C107" s="38" t="inlineStr">
+        <is>
+          <t>レート制限：`10回/分/IP`（本エンドポイントは大量の自由記述JSON行を送るため CloudFront WAF のボディ検査バイパス対象 — `.claude/rules/nestjs.md §WAF body-inspection bypass`。その分アプリ層で個別スロットリング）。上限超過時：HTTP 429 (`TOO_MANY_REQUESTS`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="B108" s="27" t="inlineStr">
         <is>
           <t>4.3 事前チェック（重複・参照整合性）</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="C107" s="38" t="inlineStr">
-        <is>
-          <t>ログインユーザーのスコープを取得する（ja_id）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="C108" s="38" t="inlineStr">
-        <is>
-          <t>rows 内の `hanbaiten_code` に重複がないことを確認する。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="C109" s="38" t="inlineStr">
         <is>
+          <t>ログインユーザーのスコープを取得する（ja_id）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="C110" s="38" t="inlineStr">
+        <is>
+          <t>rows 内の `hanbaiten_code` に重複がないことを確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="C111" s="38" t="inlineStr">
+        <is>
           <t>DBとの整合性チェックをバッチで実行する。</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="90" customHeight="1">
-      <c r="C110" s="42" t="inlineStr">
+    <row r="112" ht="90" customHeight="1">
+      <c r="C112" s="42" t="inlineStr">
         <is>
           <t>SELECT hanbaiten_id, hanbaiten_code
 FROM m_hanbaiten
@@ -10372,151 +10417,150 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D110" s="10" t="n"/>
-      <c r="E110" s="10" t="n"/>
-      <c r="F110" s="10" t="n"/>
-      <c r="G110" s="10" t="n"/>
-      <c r="H110" s="10" t="n"/>
-      <c r="I110" s="10" t="n"/>
-      <c r="J110" s="10" t="n"/>
-      <c r="K110" s="10" t="n"/>
-      <c r="L110" s="10" t="n"/>
-      <c r="M110" s="10" t="n"/>
-      <c r="N110" s="10" t="n"/>
-      <c r="O110" s="10" t="n"/>
-      <c r="P110" s="10" t="n"/>
-      <c r="Q110" s="10" t="n"/>
-      <c r="R110" s="10" t="n"/>
-      <c r="S110" s="10" t="n"/>
-      <c r="T110" s="10" t="n"/>
-      <c r="U110" s="10" t="n"/>
-      <c r="V110" s="10" t="n"/>
-      <c r="W110" s="10" t="n"/>
-      <c r="X110" s="10" t="n"/>
-      <c r="Y110" s="10" t="n"/>
-      <c r="Z110" s="10" t="n"/>
-      <c r="AA110" s="10" t="n"/>
-      <c r="AB110" s="10" t="n"/>
-      <c r="AC110" s="10" t="n"/>
-      <c r="AD110" s="10" t="n"/>
-      <c r="AE110" s="10" t="n"/>
-      <c r="AF110" s="10" t="n"/>
-      <c r="AG110" s="10" t="n"/>
-      <c r="AH110" s="10" t="n"/>
-      <c r="AI110" s="10" t="n"/>
-      <c r="AJ110" s="10" t="n"/>
-      <c r="AK110" s="11" t="n"/>
-    </row>
-    <row r="111" ht="54" customHeight="1">
-      <c r="C111" s="38" t="inlineStr">
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="10" t="n"/>
+      <c r="F112" s="10" t="n"/>
+      <c r="G112" s="10" t="n"/>
+      <c r="H112" s="10" t="n"/>
+      <c r="I112" s="10" t="n"/>
+      <c r="J112" s="10" t="n"/>
+      <c r="K112" s="10" t="n"/>
+      <c r="L112" s="10" t="n"/>
+      <c r="M112" s="10" t="n"/>
+      <c r="N112" s="10" t="n"/>
+      <c r="O112" s="10" t="n"/>
+      <c r="P112" s="10" t="n"/>
+      <c r="Q112" s="10" t="n"/>
+      <c r="R112" s="10" t="n"/>
+      <c r="S112" s="10" t="n"/>
+      <c r="T112" s="10" t="n"/>
+      <c r="U112" s="10" t="n"/>
+      <c r="V112" s="10" t="n"/>
+      <c r="W112" s="10" t="n"/>
+      <c r="X112" s="10" t="n"/>
+      <c r="Y112" s="10" t="n"/>
+      <c r="Z112" s="10" t="n"/>
+      <c r="AA112" s="10" t="n"/>
+      <c r="AB112" s="10" t="n"/>
+      <c r="AC112" s="10" t="n"/>
+      <c r="AD112" s="10" t="n"/>
+      <c r="AE112" s="10" t="n"/>
+      <c r="AF112" s="10" t="n"/>
+      <c r="AG112" s="10" t="n"/>
+      <c r="AH112" s="10" t="n"/>
+      <c r="AI112" s="10" t="n"/>
+      <c r="AJ112" s="10" t="n"/>
+      <c r="AK112" s="11" t="n"/>
+    </row>
+    <row r="113" ht="54" customHeight="1">
+      <c r="C113" s="38" t="inlineStr">
         <is>
           <t>`NEW` モード：ヒットした hanbaiten_code は「重複」エラーとする → HTTP 400 (`IMPORT_VALIDATION_ERROR`) + errors（row, field='hanbaiten_code'）</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="72" customHeight="1">
-      <c r="C112" s="38" t="inlineStr">
-        <is>
-          <t>`UPDATE_ALL` / `UPDATE_PARTIAL` モード：ヒットしなかった hanbaiten_code は「存在しない」エラーとする → HTTP 400 (`IMPORT_VALIDATION_ERROR`) + errors（row, field='hanbaiten_code'）</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="108" customHeight="1">
-      <c r="C113" s="42" t="inlineStr">
+    <row r="114" ht="54" customHeight="1">
+      <c r="C114" s="38" t="inlineStr">
+        <is>
+          <t>`UPDATE` モード：ヒットしなかった hanbaiten_code は「存在しない」エラーとする → HTTP 400 (`IMPORT_VALIDATION_ERROR`) + errors（row, field='hanbaiten_code'）</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="90" customHeight="1">
+      <c r="C115" s="42" t="inlineStr">
         <is>
           <t>SELECT tanka_id, tanka_code
 FROM m_tanka
 WHERE ja_id = :ja_id
   AND tanka_code = ANY(:tanka_codes)
-  AND tanka_type = 2  -- 配達手数料
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D113" s="10" t="n"/>
-      <c r="E113" s="10" t="n"/>
-      <c r="F113" s="10" t="n"/>
-      <c r="G113" s="10" t="n"/>
-      <c r="H113" s="10" t="n"/>
-      <c r="I113" s="10" t="n"/>
-      <c r="J113" s="10" t="n"/>
-      <c r="K113" s="10" t="n"/>
-      <c r="L113" s="10" t="n"/>
-      <c r="M113" s="10" t="n"/>
-      <c r="N113" s="10" t="n"/>
-      <c r="O113" s="10" t="n"/>
-      <c r="P113" s="10" t="n"/>
-      <c r="Q113" s="10" t="n"/>
-      <c r="R113" s="10" t="n"/>
-      <c r="S113" s="10" t="n"/>
-      <c r="T113" s="10" t="n"/>
-      <c r="U113" s="10" t="n"/>
-      <c r="V113" s="10" t="n"/>
-      <c r="W113" s="10" t="n"/>
-      <c r="X113" s="10" t="n"/>
-      <c r="Y113" s="10" t="n"/>
-      <c r="Z113" s="10" t="n"/>
-      <c r="AA113" s="10" t="n"/>
-      <c r="AB113" s="10" t="n"/>
-      <c r="AC113" s="10" t="n"/>
-      <c r="AD113" s="10" t="n"/>
-      <c r="AE113" s="10" t="n"/>
-      <c r="AF113" s="10" t="n"/>
-      <c r="AG113" s="10" t="n"/>
-      <c r="AH113" s="10" t="n"/>
-      <c r="AI113" s="10" t="n"/>
-      <c r="AJ113" s="10" t="n"/>
-      <c r="AK113" s="11" t="n"/>
-    </row>
-    <row r="114" ht="36" customHeight="1">
-      <c r="C114" s="38" t="inlineStr">
+      <c r="D115" s="10" t="n"/>
+      <c r="E115" s="10" t="n"/>
+      <c r="F115" s="10" t="n"/>
+      <c r="G115" s="10" t="n"/>
+      <c r="H115" s="10" t="n"/>
+      <c r="I115" s="10" t="n"/>
+      <c r="J115" s="10" t="n"/>
+      <c r="K115" s="10" t="n"/>
+      <c r="L115" s="10" t="n"/>
+      <c r="M115" s="10" t="n"/>
+      <c r="N115" s="10" t="n"/>
+      <c r="O115" s="10" t="n"/>
+      <c r="P115" s="10" t="n"/>
+      <c r="Q115" s="10" t="n"/>
+      <c r="R115" s="10" t="n"/>
+      <c r="S115" s="10" t="n"/>
+      <c r="T115" s="10" t="n"/>
+      <c r="U115" s="10" t="n"/>
+      <c r="V115" s="10" t="n"/>
+      <c r="W115" s="10" t="n"/>
+      <c r="X115" s="10" t="n"/>
+      <c r="Y115" s="10" t="n"/>
+      <c r="Z115" s="10" t="n"/>
+      <c r="AA115" s="10" t="n"/>
+      <c r="AB115" s="10" t="n"/>
+      <c r="AC115" s="10" t="n"/>
+      <c r="AD115" s="10" t="n"/>
+      <c r="AE115" s="10" t="n"/>
+      <c r="AF115" s="10" t="n"/>
+      <c r="AG115" s="10" t="n"/>
+      <c r="AH115" s="10" t="n"/>
+      <c r="AI115" s="10" t="n"/>
+      <c r="AJ115" s="10" t="n"/>
+      <c r="AK115" s="11" t="n"/>
+    </row>
+    <row r="116" ht="36" customHeight="1">
+      <c r="C116" s="38" t="inlineStr">
         <is>
           <t>未ヒットの tanka_code：`IMPORT_VALIDATION_ERROR` + errors（row, field='haitatsuryo_tanka_code'）</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="36" customHeight="1">
-      <c r="C115" s="38" t="inlineStr">
+    <row r="117" ht="36" customHeight="1">
+      <c r="C117" s="38" t="inlineStr">
         <is>
           <t>事前チェックエラーが存在する場合：HTTP 400 (`IMPORT_VALIDATION_ERROR`) + errors配列を返却し、以降の処理を中断する。</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="B116" s="27" t="inlineStr">
+    <row r="118" ht="18" customHeight="1">
+      <c r="B118" s="27" t="inlineStr">
         <is>
           <t>4.4 データ取込実行（トランザクション）</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="C117" s="38" t="inlineStr">
-        <is>
-          <t>DBトランザクションを開始する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="C118" s="38" t="inlineStr">
-        <is>
-          <t>以下の処理中にエラーが発生した場合は全件ロールバックする。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1">
       <c r="C119" s="38" t="inlineStr">
         <is>
+          <t>DBトランザクションを開始する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="C120" s="38" t="inlineStr">
+        <is>
+          <t>以下の処理中にエラーが発生した場合は全件ロールバックする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="C121" s="38" t="inlineStr">
+        <is>
           <t>各行に対して INSERT を実行する。</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="342" customHeight="1">
-      <c r="C120" s="42" t="inlineStr">
+    <row r="122" ht="342" customHeight="1">
+      <c r="C122" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO m_hanbaiten (
   ja_id, hanbaiten_code, hanbaiten_name, hanbaiten_name_kana, torihikisaki_no,
   yubin_no, address, tel, fax, shocho_name, itaku_kubun,
   haitatsuryo_tanka_id, haitatsuryo_shiharai_cycle,
-  tesuryo_kubun, tesuryo_amount,
+  furikomi_tesuryo_futan_kubun, furikomi_tesuryo,
   bank_code, bank_name, bank_branch_code, bank_branch_name,
   yokin_shubetsu, koza_no, koza_meigi, haiten_flg, biko,
   created_at, created_by, updated_at, updated_by
@@ -10525,7 +10569,7 @@
   :ja_id, :hanbaiten_code, :hanbaiten_name, :hanbaiten_name_kana, :torihikisaki_no,
   :yubin_no, :address, :tel, :fax, :shocho_name, :itaku_kubun,
   :haitatsuryo_tanka_id, :haitatsuryo_shiharai_cycle,
-  :tesuryo_kubun, :tesuryo_amount,
+  :furikomi_tesuryo_futan_kubun, :furikomi_tesuryo,
   :bank_code, :bank_name, :bank_branch_code, :bank_branch_name,
   :yokin_shubetsu, :koza_no, :koza_meigi, :haiten_flg, :biko,
   NOW(), :user_account_id, NOW(), :user_account_id
@@ -10533,221 +10577,138 @@
 RETURNING *</t>
         </is>
       </c>
-      <c r="D120" s="10" t="n"/>
-      <c r="E120" s="10" t="n"/>
-      <c r="F120" s="10" t="n"/>
-      <c r="G120" s="10" t="n"/>
-      <c r="H120" s="10" t="n"/>
-      <c r="I120" s="10" t="n"/>
-      <c r="J120" s="10" t="n"/>
-      <c r="K120" s="10" t="n"/>
-      <c r="L120" s="10" t="n"/>
-      <c r="M120" s="10" t="n"/>
-      <c r="N120" s="10" t="n"/>
-      <c r="O120" s="10" t="n"/>
-      <c r="P120" s="10" t="n"/>
-      <c r="Q120" s="10" t="n"/>
-      <c r="R120" s="10" t="n"/>
-      <c r="S120" s="10" t="n"/>
-      <c r="T120" s="10" t="n"/>
-      <c r="U120" s="10" t="n"/>
-      <c r="V120" s="10" t="n"/>
-      <c r="W120" s="10" t="n"/>
-      <c r="X120" s="10" t="n"/>
-      <c r="Y120" s="10" t="n"/>
-      <c r="Z120" s="10" t="n"/>
-      <c r="AA120" s="10" t="n"/>
-      <c r="AB120" s="10" t="n"/>
-      <c r="AC120" s="10" t="n"/>
-      <c r="AD120" s="10" t="n"/>
-      <c r="AE120" s="10" t="n"/>
-      <c r="AF120" s="10" t="n"/>
-      <c r="AG120" s="10" t="n"/>
-      <c r="AH120" s="10" t="n"/>
-      <c r="AI120" s="10" t="n"/>
-      <c r="AJ120" s="10" t="n"/>
-      <c r="AK120" s="11" t="n"/>
-    </row>
-    <row r="121" ht="36" customHeight="1">
-      <c r="C121" s="38" t="inlineStr">
+      <c r="D122" s="10" t="n"/>
+      <c r="E122" s="10" t="n"/>
+      <c r="F122" s="10" t="n"/>
+      <c r="G122" s="10" t="n"/>
+      <c r="H122" s="10" t="n"/>
+      <c r="I122" s="10" t="n"/>
+      <c r="J122" s="10" t="n"/>
+      <c r="K122" s="10" t="n"/>
+      <c r="L122" s="10" t="n"/>
+      <c r="M122" s="10" t="n"/>
+      <c r="N122" s="10" t="n"/>
+      <c r="O122" s="10" t="n"/>
+      <c r="P122" s="10" t="n"/>
+      <c r="Q122" s="10" t="n"/>
+      <c r="R122" s="10" t="n"/>
+      <c r="S122" s="10" t="n"/>
+      <c r="T122" s="10" t="n"/>
+      <c r="U122" s="10" t="n"/>
+      <c r="V122" s="10" t="n"/>
+      <c r="W122" s="10" t="n"/>
+      <c r="X122" s="10" t="n"/>
+      <c r="Y122" s="10" t="n"/>
+      <c r="Z122" s="10" t="n"/>
+      <c r="AA122" s="10" t="n"/>
+      <c r="AB122" s="10" t="n"/>
+      <c r="AC122" s="10" t="n"/>
+      <c r="AD122" s="10" t="n"/>
+      <c r="AE122" s="10" t="n"/>
+      <c r="AF122" s="10" t="n"/>
+      <c r="AG122" s="10" t="n"/>
+      <c r="AH122" s="10" t="n"/>
+      <c r="AI122" s="10" t="n"/>
+      <c r="AJ122" s="10" t="n"/>
+      <c r="AK122" s="11" t="n"/>
+    </row>
+    <row r="123" ht="36" customHeight="1">
+      <c r="C123" s="38" t="inlineStr">
         <is>
           <t>selected_columns に含まれない列はデフォルト値（空文字 / NULL / false）を設定する。</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="36" customHeight="1">
-      <c r="C122" s="38" t="inlineStr">
-        <is>
-          <t>各行に対して既存レコードを取得後、selected_columns 対象外の項目も含めて更新する（未選択列は NULL / 空文字で上書き）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="409" customHeight="1">
-      <c r="C123" s="42" t="inlineStr">
-        <is>
-          <t>-- 更新前データ取得（操作ログ用）
-SELECT * FROM m_hanbaiten
-WHERE ja_id = :ja_id
-  AND hanbaiten_code = :hanbaiten_code
-  AND deleted_at IS NULL
--- 更新
-UPDATE m_hanbaiten
-SET hanbaiten_name = :hanbaiten_name,
-    hanbaiten_name_kana = :hanbaiten_name_kana,
-    torihikisaki_no = :torihikisaki_no,
-    yubin_no = :yubin_no,
-    address = :address,
-    tel = :tel,
-    fax = :fax,
-    shocho_name = :shocho_name,
-    itaku_kubun = :itaku_kubun,
-    haitatsuryo_tanka_id = :haitatsuryo_tanka_id,
-    haitatsuryo_shiharai_cycle = :haitatsuryo_shiharai_cycle,
-    tesuryo_kubun = :tesuryo_kubun,
-    tesuryo_amount = :tesuryo_amount,
-    bank_code = :bank_code,
-    bank_name = :bank_name,
-    bank_branch_code = :bank_branch_code,
-    bank_branch_name = :bank_branch_name,
-    yokin_shubetsu = :yokin_shubetsu,
-    koza_no = :koza_no,
-    koza_meigi = :koza_meigi,
-    haiten_flg = :haiten_flg,
-    biko = :biko,
-    updated_at = NOW(),
-    updated_by = :user_account_id
-WHERE ja_id = :ja_id
-  AND hanbaiten_code = :hanbaiten_code
-  AND deleted_at IS NULL
-RETURNING *</t>
-        </is>
-      </c>
-      <c r="D123" s="10" t="n"/>
-      <c r="E123" s="10" t="n"/>
-      <c r="F123" s="10" t="n"/>
-      <c r="G123" s="10" t="n"/>
-      <c r="H123" s="10" t="n"/>
-      <c r="I123" s="10" t="n"/>
-      <c r="J123" s="10" t="n"/>
-      <c r="K123" s="10" t="n"/>
-      <c r="L123" s="10" t="n"/>
-      <c r="M123" s="10" t="n"/>
-      <c r="N123" s="10" t="n"/>
-      <c r="O123" s="10" t="n"/>
-      <c r="P123" s="10" t="n"/>
-      <c r="Q123" s="10" t="n"/>
-      <c r="R123" s="10" t="n"/>
-      <c r="S123" s="10" t="n"/>
-      <c r="T123" s="10" t="n"/>
-      <c r="U123" s="10" t="n"/>
-      <c r="V123" s="10" t="n"/>
-      <c r="W123" s="10" t="n"/>
-      <c r="X123" s="10" t="n"/>
-      <c r="Y123" s="10" t="n"/>
-      <c r="Z123" s="10" t="n"/>
-      <c r="AA123" s="10" t="n"/>
-      <c r="AB123" s="10" t="n"/>
-      <c r="AC123" s="10" t="n"/>
-      <c r="AD123" s="10" t="n"/>
-      <c r="AE123" s="10" t="n"/>
-      <c r="AF123" s="10" t="n"/>
-      <c r="AG123" s="10" t="n"/>
-      <c r="AH123" s="10" t="n"/>
-      <c r="AI123" s="10" t="n"/>
-      <c r="AJ123" s="10" t="n"/>
-      <c r="AK123" s="11" t="n"/>
-    </row>
-    <row r="124" ht="18" customHeight="1">
+    <row r="124" ht="72" customHeight="1">
       <c r="C124" s="38" t="inlineStr">
         <is>
-          <t>selected_columns に含まれる列のみ更新する。未選択列は既存値を維持する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="18" customHeight="1">
+          <t>selected_columns に含まれる列のみ更新する（`hanbaiten_code` はキー列のため SET 対象から除外）。未選択列は既存値を維持する。全項目を更新したい場合は全列を selected_columns に含める（2026-07 顧客要件により旧 `UPDATE_ALL` / `UPDATE_PARTIAL` の2区分は本モードに統合済み）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="36" customHeight="1">
       <c r="C125" s="38" t="inlineStr">
         <is>
-          <t>動的に SET 句を構築する（擬似コード）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="270" customHeight="1">
-      <c r="C126" s="42" t="inlineStr">
-        <is>
-          <t>-- 更新前データ取得（操作ログ用）
-SELECT * FROM m_hanbaiten
-WHERE ja_id = :ja_id
-  AND hanbaiten_code = :hanbaiten_code
-  AND deleted_at IS NULL
--- 動的 UPDATE（selected_columns に含まれる項目のみ SET）
+          <t>動的に SET 句を構築する（擬似コード）。selected_columns の空セルは列の既定値（空文字 / false。NULL許容の数値・区分列は NULL）にフォールバックする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="54" customHeight="1">
+      <c r="C126" s="38" t="inlineStr">
+        <is>
+          <t>`haitatsuryo_tanka_code` が selected_columns に含まれる場合は 4.3.2 で解決した tanka_id を `haitatsuryo_tanka_id` に設定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="108" customHeight="1">
+      <c r="C127" s="42" t="inlineStr">
+        <is>
+          <t>-- 動的 UPDATE（selected_columns に含まれる項目のみ SET）
 UPDATE m_hanbaiten
 SET {dynamic_set_clause},
     updated_at = NOW(),
     updated_by = :user_account_id
-WHERE ja_id = :ja_id
-  AND hanbaiten_code = :hanbaiten_code
-  AND deleted_at IS NULL
-RETURNING *</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="n"/>
-      <c r="E126" s="10" t="n"/>
-      <c r="F126" s="10" t="n"/>
-      <c r="G126" s="10" t="n"/>
-      <c r="H126" s="10" t="n"/>
-      <c r="I126" s="10" t="n"/>
-      <c r="J126" s="10" t="n"/>
-      <c r="K126" s="10" t="n"/>
-      <c r="L126" s="10" t="n"/>
-      <c r="M126" s="10" t="n"/>
-      <c r="N126" s="10" t="n"/>
-      <c r="O126" s="10" t="n"/>
-      <c r="P126" s="10" t="n"/>
-      <c r="Q126" s="10" t="n"/>
-      <c r="R126" s="10" t="n"/>
-      <c r="S126" s="10" t="n"/>
-      <c r="T126" s="10" t="n"/>
-      <c r="U126" s="10" t="n"/>
-      <c r="V126" s="10" t="n"/>
-      <c r="W126" s="10" t="n"/>
-      <c r="X126" s="10" t="n"/>
-      <c r="Y126" s="10" t="n"/>
-      <c r="Z126" s="10" t="n"/>
-      <c r="AA126" s="10" t="n"/>
-      <c r="AB126" s="10" t="n"/>
-      <c r="AC126" s="10" t="n"/>
-      <c r="AD126" s="10" t="n"/>
-      <c r="AE126" s="10" t="n"/>
-      <c r="AF126" s="10" t="n"/>
-      <c r="AG126" s="10" t="n"/>
-      <c r="AH126" s="10" t="n"/>
-      <c r="AI126" s="10" t="n"/>
-      <c r="AJ126" s="10" t="n"/>
-      <c r="AK126" s="11" t="n"/>
-    </row>
-    <row r="127" ht="54" customHeight="1">
-      <c r="C127" s="38" t="inlineStr">
+WHERE hanbaiten_id = :hanbaiten_id</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="n"/>
+      <c r="E127" s="10" t="n"/>
+      <c r="F127" s="10" t="n"/>
+      <c r="G127" s="10" t="n"/>
+      <c r="H127" s="10" t="n"/>
+      <c r="I127" s="10" t="n"/>
+      <c r="J127" s="10" t="n"/>
+      <c r="K127" s="10" t="n"/>
+      <c r="L127" s="10" t="n"/>
+      <c r="M127" s="10" t="n"/>
+      <c r="N127" s="10" t="n"/>
+      <c r="O127" s="10" t="n"/>
+      <c r="P127" s="10" t="n"/>
+      <c r="Q127" s="10" t="n"/>
+      <c r="R127" s="10" t="n"/>
+      <c r="S127" s="10" t="n"/>
+      <c r="T127" s="10" t="n"/>
+      <c r="U127" s="10" t="n"/>
+      <c r="V127" s="10" t="n"/>
+      <c r="W127" s="10" t="n"/>
+      <c r="X127" s="10" t="n"/>
+      <c r="Y127" s="10" t="n"/>
+      <c r="Z127" s="10" t="n"/>
+      <c r="AA127" s="10" t="n"/>
+      <c r="AB127" s="10" t="n"/>
+      <c r="AC127" s="10" t="n"/>
+      <c r="AD127" s="10" t="n"/>
+      <c r="AE127" s="10" t="n"/>
+      <c r="AF127" s="10" t="n"/>
+      <c r="AG127" s="10" t="n"/>
+      <c r="AH127" s="10" t="n"/>
+      <c r="AI127" s="10" t="n"/>
+      <c r="AJ127" s="10" t="n"/>
+      <c r="AK127" s="11" t="n"/>
+    </row>
+    <row r="128" ht="54" customHeight="1">
+      <c r="C128" s="38" t="inlineStr">
         <is>
           <t>実行中に DB 制約違反等が発生した場合：トランザクションを即時ロールバックし、HTTP 400 (`IMPORT_VALIDATION_ERROR`) または HTTP 500 (`INTERNAL_SERVER_ERROR`) を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="B128" s="27" t="inlineStr">
+    <row r="129" ht="18" customHeight="1">
+      <c r="B129" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="36" customHeight="1">
-      <c r="C129" s="38" t="inlineStr">
+    <row r="130" ht="36" customHeight="1">
+      <c r="C130" s="38" t="inlineStr">
         <is>
           <t>全行の処理が完了した後、一括取込操作の操作ログを記録する（行単位ではなく取込バッチ単位で1件記録する）。</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="216" customHeight="1">
-      <c r="C130" s="42" t="inlineStr">
+    <row r="131" ht="216" customHeight="1">
+      <c r="C131" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -10763,85 +10724,85 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D130" s="10" t="n"/>
-      <c r="E130" s="10" t="n"/>
-      <c r="F130" s="10" t="n"/>
-      <c r="G130" s="10" t="n"/>
-      <c r="H130" s="10" t="n"/>
-      <c r="I130" s="10" t="n"/>
-      <c r="J130" s="10" t="n"/>
-      <c r="K130" s="10" t="n"/>
-      <c r="L130" s="10" t="n"/>
-      <c r="M130" s="10" t="n"/>
-      <c r="N130" s="10" t="n"/>
-      <c r="O130" s="10" t="n"/>
-      <c r="P130" s="10" t="n"/>
-      <c r="Q130" s="10" t="n"/>
-      <c r="R130" s="10" t="n"/>
-      <c r="S130" s="10" t="n"/>
-      <c r="T130" s="10" t="n"/>
-      <c r="U130" s="10" t="n"/>
-      <c r="V130" s="10" t="n"/>
-      <c r="W130" s="10" t="n"/>
-      <c r="X130" s="10" t="n"/>
-      <c r="Y130" s="10" t="n"/>
-      <c r="Z130" s="10" t="n"/>
-      <c r="AA130" s="10" t="n"/>
-      <c r="AB130" s="10" t="n"/>
-      <c r="AC130" s="10" t="n"/>
-      <c r="AD130" s="10" t="n"/>
-      <c r="AE130" s="10" t="n"/>
-      <c r="AF130" s="10" t="n"/>
-      <c r="AG130" s="10" t="n"/>
-      <c r="AH130" s="10" t="n"/>
-      <c r="AI130" s="10" t="n"/>
-      <c r="AJ130" s="10" t="n"/>
-      <c r="AK130" s="11" t="n"/>
-    </row>
-    <row r="131" ht="54" customHeight="1">
-      <c r="C131" s="38" t="inlineStr">
-        <is>
-          <t>`:operation_label`：`IMPORT_NEW` / `IMPORT_UPDATE_ALL` / `IMPORT_UPDATE_PARTIAL` のいずれか（import_mode に対応）</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1">
+      <c r="D131" s="10" t="n"/>
+      <c r="E131" s="10" t="n"/>
+      <c r="F131" s="10" t="n"/>
+      <c r="G131" s="10" t="n"/>
+      <c r="H131" s="10" t="n"/>
+      <c r="I131" s="10" t="n"/>
+      <c r="J131" s="10" t="n"/>
+      <c r="K131" s="10" t="n"/>
+      <c r="L131" s="10" t="n"/>
+      <c r="M131" s="10" t="n"/>
+      <c r="N131" s="10" t="n"/>
+      <c r="O131" s="10" t="n"/>
+      <c r="P131" s="10" t="n"/>
+      <c r="Q131" s="10" t="n"/>
+      <c r="R131" s="10" t="n"/>
+      <c r="S131" s="10" t="n"/>
+      <c r="T131" s="10" t="n"/>
+      <c r="U131" s="10" t="n"/>
+      <c r="V131" s="10" t="n"/>
+      <c r="W131" s="10" t="n"/>
+      <c r="X131" s="10" t="n"/>
+      <c r="Y131" s="10" t="n"/>
+      <c r="Z131" s="10" t="n"/>
+      <c r="AA131" s="10" t="n"/>
+      <c r="AB131" s="10" t="n"/>
+      <c r="AC131" s="10" t="n"/>
+      <c r="AD131" s="10" t="n"/>
+      <c r="AE131" s="10" t="n"/>
+      <c r="AF131" s="10" t="n"/>
+      <c r="AG131" s="10" t="n"/>
+      <c r="AH131" s="10" t="n"/>
+      <c r="AI131" s="10" t="n"/>
+      <c r="AJ131" s="10" t="n"/>
+      <c r="AK131" s="11" t="n"/>
+    </row>
+    <row r="132" ht="72" customHeight="1">
       <c r="C132" s="38" t="inlineStr">
         <is>
+          <t>`:operation_label`：`IMPORT_NEW` / `IMPORT_UPDATE_PARTIAL` のいずれか（import_mode `NEW` / `UPDATE` に対応。`UPDATE` は過去ログ互換のため `IMPORT_UPDATE_PARTIAL` ラベルを継続使用する）</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="C133" s="38" t="inlineStr">
+        <is>
           <t>`before_value`：</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="D133" s="38" t="inlineStr">
-        <is>
-          <t>`NEW` モード：空文字列</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="36" customHeight="1">
+    <row r="134" ht="18" customHeight="1">
       <c r="D134" s="38" t="inlineStr">
         <is>
-          <t>`UPDATE_ALL` / `UPDATE_PARTIAL` モード：更新前データのサマリJSON `{ "rows": [{...}, ...] }`（各行の更新前状態を格納）</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="54" customHeight="1">
-      <c r="C135" s="38" t="inlineStr">
-        <is>
-          <t>`after_value`：取込結果サマリJSON `{ "import_mode", "total_rows", "created_count", "updated_count", "created_ids": [...], "updated_ids": [...] }`</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="18" customHeight="1">
+          <t>`NEW` モード：省略（記録しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="36" customHeight="1">
+      <c r="D135" s="38" t="inlineStr">
+        <is>
+          <t>`UPDATE` モード：`{ "import_mode": "UPDATE", "target_codes": [...] }`（取込対象の hanbaiten_code 一覧）</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="54" customHeight="1">
       <c r="C136" s="38" t="inlineStr">
         <is>
+          <t>`after_value`：取込結果サマリJSON `{ "import_mode", "total_rows", "created_count", "updated_count", "created_ids": [...], "imported_at" }`</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="C137" s="38" t="inlineStr">
+        <is>
           <t>パスワード等の機密情報は含めないこと。</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="144" customHeight="1">
-      <c r="C137" s="42" t="inlineStr">
+    <row r="138" ht="144" customHeight="1">
+      <c r="C138" s="42" t="inlineStr">
         <is>
           <t>{
   "import_mode": "NEW",
@@ -10849,103 +10810,103 @@
   "created_count": 2,
   "updated_count": 0,
   "created_ids": [101, 102],
-  "updated_ids": []
+  "imported_at": "2026-04-22T10:00:00.000Z"
 }</t>
         </is>
       </c>
-      <c r="D137" s="10" t="n"/>
-      <c r="E137" s="10" t="n"/>
-      <c r="F137" s="10" t="n"/>
-      <c r="G137" s="10" t="n"/>
-      <c r="H137" s="10" t="n"/>
-      <c r="I137" s="10" t="n"/>
-      <c r="J137" s="10" t="n"/>
-      <c r="K137" s="10" t="n"/>
-      <c r="L137" s="10" t="n"/>
-      <c r="M137" s="10" t="n"/>
-      <c r="N137" s="10" t="n"/>
-      <c r="O137" s="10" t="n"/>
-      <c r="P137" s="10" t="n"/>
-      <c r="Q137" s="10" t="n"/>
-      <c r="R137" s="10" t="n"/>
-      <c r="S137" s="10" t="n"/>
-      <c r="T137" s="10" t="n"/>
-      <c r="U137" s="10" t="n"/>
-      <c r="V137" s="10" t="n"/>
-      <c r="W137" s="10" t="n"/>
-      <c r="X137" s="10" t="n"/>
-      <c r="Y137" s="10" t="n"/>
-      <c r="Z137" s="10" t="n"/>
-      <c r="AA137" s="10" t="n"/>
-      <c r="AB137" s="10" t="n"/>
-      <c r="AC137" s="10" t="n"/>
-      <c r="AD137" s="10" t="n"/>
-      <c r="AE137" s="10" t="n"/>
-      <c r="AF137" s="10" t="n"/>
-      <c r="AG137" s="10" t="n"/>
-      <c r="AH137" s="10" t="n"/>
-      <c r="AI137" s="10" t="n"/>
-      <c r="AJ137" s="10" t="n"/>
-      <c r="AK137" s="11" t="n"/>
-    </row>
-    <row r="138" ht="18" customHeight="1">
-      <c r="B138" s="27" t="inlineStr">
+      <c r="D138" s="10" t="n"/>
+      <c r="E138" s="10" t="n"/>
+      <c r="F138" s="10" t="n"/>
+      <c r="G138" s="10" t="n"/>
+      <c r="H138" s="10" t="n"/>
+      <c r="I138" s="10" t="n"/>
+      <c r="J138" s="10" t="n"/>
+      <c r="K138" s="10" t="n"/>
+      <c r="L138" s="10" t="n"/>
+      <c r="M138" s="10" t="n"/>
+      <c r="N138" s="10" t="n"/>
+      <c r="O138" s="10" t="n"/>
+      <c r="P138" s="10" t="n"/>
+      <c r="Q138" s="10" t="n"/>
+      <c r="R138" s="10" t="n"/>
+      <c r="S138" s="10" t="n"/>
+      <c r="T138" s="10" t="n"/>
+      <c r="U138" s="10" t="n"/>
+      <c r="V138" s="10" t="n"/>
+      <c r="W138" s="10" t="n"/>
+      <c r="X138" s="10" t="n"/>
+      <c r="Y138" s="10" t="n"/>
+      <c r="Z138" s="10" t="n"/>
+      <c r="AA138" s="10" t="n"/>
+      <c r="AB138" s="10" t="n"/>
+      <c r="AC138" s="10" t="n"/>
+      <c r="AD138" s="10" t="n"/>
+      <c r="AE138" s="10" t="n"/>
+      <c r="AF138" s="10" t="n"/>
+      <c r="AG138" s="10" t="n"/>
+      <c r="AH138" s="10" t="n"/>
+      <c r="AI138" s="10" t="n"/>
+      <c r="AJ138" s="10" t="n"/>
+      <c r="AK138" s="11" t="n"/>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="B139" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="18" customHeight="1">
-      <c r="C139" s="38" t="inlineStr">
-        <is>
-          <t>トランザクションをコミットする。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="18" customHeight="1">
       <c r="C140" s="38" t="inlineStr">
         <is>
-          <t>取込結果サマリを data オブジェクトとして返却する。HTTP 200。</t>
+          <t>トランザクションをコミットする。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="18" customHeight="1">
       <c r="C141" s="38" t="inlineStr">
         <is>
-          <t>message: `正常に取り込みました。`（ACSMS-MSG-007-004）</t>
+          <t>取込結果サマリを data オブジェクトとして返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="18" customHeight="1">
-      <c r="B142" s="27" t="inlineStr">
+      <c r="C142" s="38" t="inlineStr">
+        <is>
+          <t>message: `取り込みました。`（ACSMS-MSG-007-004）</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="B143" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="18" customHeight="1">
-      <c r="C143" s="38" t="inlineStr">
-        <is>
-          <t>取込処理中にエラーが発生した場合、トランザクションを全件ロールバックする。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="C144" s="38" t="inlineStr">
         <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+          <t>取込処理中にエラーが発生した場合、トランザクションを全件ロールバックする。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="18" customHeight="1">
       <c r="C145" s="38" t="inlineStr">
         <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="C146" s="38" t="inlineStr">
+        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="216" customHeight="1">
-      <c r="C146" s="42" t="inlineStr">
+    <row r="147" ht="216" customHeight="1">
+      <c r="C147" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -10961,73 +10922,66 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D146" s="10" t="n"/>
-      <c r="E146" s="10" t="n"/>
-      <c r="F146" s="10" t="n"/>
-      <c r="G146" s="10" t="n"/>
-      <c r="H146" s="10" t="n"/>
-      <c r="I146" s="10" t="n"/>
-      <c r="J146" s="10" t="n"/>
-      <c r="K146" s="10" t="n"/>
-      <c r="L146" s="10" t="n"/>
-      <c r="M146" s="10" t="n"/>
-      <c r="N146" s="10" t="n"/>
-      <c r="O146" s="10" t="n"/>
-      <c r="P146" s="10" t="n"/>
-      <c r="Q146" s="10" t="n"/>
-      <c r="R146" s="10" t="n"/>
-      <c r="S146" s="10" t="n"/>
-      <c r="T146" s="10" t="n"/>
-      <c r="U146" s="10" t="n"/>
-      <c r="V146" s="10" t="n"/>
-      <c r="W146" s="10" t="n"/>
-      <c r="X146" s="10" t="n"/>
-      <c r="Y146" s="10" t="n"/>
-      <c r="Z146" s="10" t="n"/>
-      <c r="AA146" s="10" t="n"/>
-      <c r="AB146" s="10" t="n"/>
-      <c r="AC146" s="10" t="n"/>
-      <c r="AD146" s="10" t="n"/>
-      <c r="AE146" s="10" t="n"/>
-      <c r="AF146" s="10" t="n"/>
-      <c r="AG146" s="10" t="n"/>
-      <c r="AH146" s="10" t="n"/>
-      <c r="AI146" s="10" t="n"/>
-      <c r="AJ146" s="10" t="n"/>
-      <c r="AK146" s="11" t="n"/>
+      <c r="D147" s="10" t="n"/>
+      <c r="E147" s="10" t="n"/>
+      <c r="F147" s="10" t="n"/>
+      <c r="G147" s="10" t="n"/>
+      <c r="H147" s="10" t="n"/>
+      <c r="I147" s="10" t="n"/>
+      <c r="J147" s="10" t="n"/>
+      <c r="K147" s="10" t="n"/>
+      <c r="L147" s="10" t="n"/>
+      <c r="M147" s="10" t="n"/>
+      <c r="N147" s="10" t="n"/>
+      <c r="O147" s="10" t="n"/>
+      <c r="P147" s="10" t="n"/>
+      <c r="Q147" s="10" t="n"/>
+      <c r="R147" s="10" t="n"/>
+      <c r="S147" s="10" t="n"/>
+      <c r="T147" s="10" t="n"/>
+      <c r="U147" s="10" t="n"/>
+      <c r="V147" s="10" t="n"/>
+      <c r="W147" s="10" t="n"/>
+      <c r="X147" s="10" t="n"/>
+      <c r="Y147" s="10" t="n"/>
+      <c r="Z147" s="10" t="n"/>
+      <c r="AA147" s="10" t="n"/>
+      <c r="AB147" s="10" t="n"/>
+      <c r="AC147" s="10" t="n"/>
+      <c r="AD147" s="10" t="n"/>
+      <c r="AE147" s="10" t="n"/>
+      <c r="AF147" s="10" t="n"/>
+      <c r="AG147" s="10" t="n"/>
+      <c r="AH147" s="10" t="n"/>
+      <c r="AI147" s="10" t="n"/>
+      <c r="AJ147" s="10" t="n"/>
+      <c r="AK147" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="364">
+  <mergeCells count="366">
     <mergeCell ref="Y46:AB46"/>
     <mergeCell ref="D134:AK134"/>
-    <mergeCell ref="T24:X24"/>
     <mergeCell ref="D61:L61"/>
     <mergeCell ref="Y48:AB48"/>
     <mergeCell ref="Y41:AB41"/>
-    <mergeCell ref="D56:L56"/>
+    <mergeCell ref="D62:L62"/>
+    <mergeCell ref="C128:AK128"/>
     <mergeCell ref="T55:X55"/>
     <mergeCell ref="M59:P59"/>
     <mergeCell ref="Y43:AB43"/>
     <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="C65:AK65"/>
-    <mergeCell ref="B73:I73"/>
-    <mergeCell ref="C56:C61"/>
+    <mergeCell ref="C142:AK142"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="C80:AK80"/>
-    <mergeCell ref="C129:AK129"/>
     <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="M54:P54"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B68:I68"/>
     <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="B138:AK138"/>
     <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="T37:X37"/>
-    <mergeCell ref="B76:I76"/>
     <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="A89:AK89"/>
     <mergeCell ref="Y36:AB36"/>
     <mergeCell ref="C131:AK131"/>
     <mergeCell ref="AC39:AE39"/>
@@ -11046,21 +11000,25 @@
     <mergeCell ref="C117:AK117"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C35:L35"/>
+    <mergeCell ref="Y51:AB51"/>
     <mergeCell ref="C115:AK115"/>
-    <mergeCell ref="B64:I64"/>
     <mergeCell ref="C144:AK144"/>
-    <mergeCell ref="B90:AK90"/>
+    <mergeCell ref="C57:C62"/>
     <mergeCell ref="M27:P27"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="T45:X45"/>
     <mergeCell ref="C145:AK145"/>
-    <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="B14:I21"/>
     <mergeCell ref="Y33:AB33"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C28:L28"/>
     <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="B77:I77"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q49:S49"/>
     <mergeCell ref="Q36:S36"/>
@@ -11070,25 +11028,26 @@
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="D94:AK94"/>
     <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="B108:AK108"/>
+    <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
+    <mergeCell ref="B143:AK143"/>
     <mergeCell ref="Y39:AB39"/>
     <mergeCell ref="AF56:AK56"/>
-    <mergeCell ref="C54:L54"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="C41:L41"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="Q62:S62"/>
     <mergeCell ref="C119:AK119"/>
+    <mergeCell ref="C56:L56"/>
     <mergeCell ref="C43:L43"/>
-    <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
     <mergeCell ref="M41:P41"/>
-    <mergeCell ref="M24:P24"/>
     <mergeCell ref="T35:X35"/>
-    <mergeCell ref="A22:AK22"/>
     <mergeCell ref="D58:L58"/>
+    <mergeCell ref="C147:AK147"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
@@ -11096,19 +11055,19 @@
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C44:L44"/>
     <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C71:AK71"/>
     <mergeCell ref="D95:AK95"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="M46:P46"/>
     <mergeCell ref="M37:P37"/>
+    <mergeCell ref="D97:AK97"/>
     <mergeCell ref="AC30:AE30"/>
     <mergeCell ref="M61:P61"/>
+    <mergeCell ref="C66:AK66"/>
     <mergeCell ref="C102:AK102"/>
-    <mergeCell ref="C77:AK77"/>
     <mergeCell ref="J18:M18"/>
-    <mergeCell ref="C68:AK68"/>
+    <mergeCell ref="A53:AK53"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="C49:L49"/>
     <mergeCell ref="M56:P56"/>
@@ -11117,14 +11076,14 @@
     <mergeCell ref="AF50:AK50"/>
     <mergeCell ref="C42:L42"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C143:AK143"/>
+    <mergeCell ref="B139:AK139"/>
     <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="Q58:S58"/>
     <mergeCell ref="C39:L39"/>
-    <mergeCell ref="D103:AK103"/>
+    <mergeCell ref="N21:AK21"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="Q60:S60"/>
     <mergeCell ref="M62:P62"/>
@@ -11132,24 +11091,27 @@
     <mergeCell ref="AC42:AE42"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="B86:I86"/>
     <mergeCell ref="AC44:AE44"/>
-    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="C118:AK118"/>
+    <mergeCell ref="C103:AK103"/>
+    <mergeCell ref="M51:P51"/>
+    <mergeCell ref="C63:L63"/>
     <mergeCell ref="C50:L50"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
-    <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="T46:X46"/>
     <mergeCell ref="Y49:AB49"/>
     <mergeCell ref="T48:X48"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="C98:AK98"/>
     <mergeCell ref="AF42:AK42"/>
+    <mergeCell ref="C116:AK116"/>
     <mergeCell ref="M34:P34"/>
-    <mergeCell ref="B67:I67"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
+    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="V1:Y1"/>
@@ -11164,9 +11126,9 @@
     <mergeCell ref="AC47:AE47"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="D57:L57"/>
+    <mergeCell ref="AF63:AK63"/>
     <mergeCell ref="C111:AK111"/>
     <mergeCell ref="Y61:AE61"/>
-    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="M58:P58"/>
     <mergeCell ref="AC50:AE50"/>
@@ -11175,11 +11137,12 @@
     <mergeCell ref="C137:AK137"/>
     <mergeCell ref="C124:AK124"/>
     <mergeCell ref="Y44:AB44"/>
-    <mergeCell ref="C139:AK139"/>
     <mergeCell ref="D60:L60"/>
     <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="C138:AK138"/>
     <mergeCell ref="C132:AK132"/>
     <mergeCell ref="Y59:AE59"/>
+    <mergeCell ref="A90:AK90"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
@@ -11188,30 +11151,30 @@
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="AC38:AE38"/>
     <mergeCell ref="Y32:AB32"/>
-    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="B70:I70"/>
     <mergeCell ref="AC46:AE46"/>
     <mergeCell ref="Y47:AB47"/>
     <mergeCell ref="AC40:AE40"/>
     <mergeCell ref="C34:L34"/>
     <mergeCell ref="C112:AK112"/>
     <mergeCell ref="C109:AK109"/>
-    <mergeCell ref="B82:I82"/>
     <mergeCell ref="Y62:AE62"/>
+    <mergeCell ref="C84:AK84"/>
+    <mergeCell ref="C133:AK133"/>
     <mergeCell ref="C127:AK127"/>
-    <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="AC41:AE41"/>
     <mergeCell ref="C114:AK114"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B65:I65"/>
     <mergeCell ref="Y50:AB50"/>
+    <mergeCell ref="B83:I83"/>
     <mergeCell ref="N20:AK20"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="B91:AK91"/>
-    <mergeCell ref="B85:I85"/>
+    <mergeCell ref="D135:AK135"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="T57:X57"/>
     <mergeCell ref="AC43:AE43"/>
@@ -11221,17 +11184,15 @@
     <mergeCell ref="AF59:AK59"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="C104:AK104"/>
     <mergeCell ref="T58:X58"/>
-    <mergeCell ref="T54:X54"/>
     <mergeCell ref="Y42:AB42"/>
     <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="C99:AK99"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="AC48:AE48"/>
@@ -11241,11 +11202,12 @@
     <mergeCell ref="T60:X60"/>
     <mergeCell ref="C130:AK130"/>
     <mergeCell ref="C55:L55"/>
-    <mergeCell ref="B106:AK106"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C122:AK122"/>
+    <mergeCell ref="C72:AK72"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="C125:AK125"/>
+    <mergeCell ref="Q63:S63"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="C136:AK136"/>
     <mergeCell ref="Y57:AE57"/>
@@ -11259,6 +11221,7 @@
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="C146:AK146"/>
+    <mergeCell ref="B92:AK92"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="C105:AK105"/>
     <mergeCell ref="D96:AK96"/>
@@ -11266,15 +11229,13 @@
     <mergeCell ref="C120:AK120"/>
     <mergeCell ref="Y60:AE60"/>
     <mergeCell ref="N16:AK16"/>
-    <mergeCell ref="B79:I79"/>
     <mergeCell ref="Q55:S55"/>
     <mergeCell ref="Y37:AB37"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="D93:AK93"/>
+    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="AF47:AK47"/>
@@ -11287,73 +11248,74 @@
     <mergeCell ref="AF61:AK61"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="C40:L40"/>
+    <mergeCell ref="B100:AK100"/>
+    <mergeCell ref="D104:AK104"/>
+    <mergeCell ref="C51:L51"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="M57:P57"/>
     <mergeCell ref="M32:P32"/>
     <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
-    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="N17:AK17"/>
+    <mergeCell ref="T63:X63"/>
     <mergeCell ref="Y38:AB38"/>
     <mergeCell ref="N19:AK19"/>
-    <mergeCell ref="B128:AK128"/>
-    <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q56:S56"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
+    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="C46:L46"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="C48:L48"/>
     <mergeCell ref="AF62:AK62"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="C101:AK101"/>
+    <mergeCell ref="A23:AK23"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="B116:AK116"/>
-    <mergeCell ref="A52:AK52"/>
+    <mergeCell ref="AF51:AK51"/>
+    <mergeCell ref="Y63:AE63"/>
     <mergeCell ref="M44:P44"/>
+    <mergeCell ref="B118:AK118"/>
+    <mergeCell ref="AC51:AE51"/>
     <mergeCell ref="AF38:AK38"/>
-    <mergeCell ref="B14:I20"/>
     <mergeCell ref="M60:P60"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
-    <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="B129:AK129"/>
     <mergeCell ref="C36:L36"/>
+    <mergeCell ref="Q51:S51"/>
     <mergeCell ref="AC33:AE33"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="J7:AK7"/>
+    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="T32:X32"/>
     <mergeCell ref="AC35:AE35"/>
+    <mergeCell ref="M63:P63"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="AC34:AE34"/>
     <mergeCell ref="M50:P50"/>
     <mergeCell ref="C107:AK107"/>
-    <mergeCell ref="D133:AK133"/>
     <mergeCell ref="M55:P55"/>
-    <mergeCell ref="C62:L62"/>
     <mergeCell ref="C121:AK121"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="B142:AK142"/>
     <mergeCell ref="Y40:AB40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="C135:AK135"/>
-    <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
-    <mergeCell ref="C92:AK92"/>
+    <mergeCell ref="B71:I71"/>
     <mergeCell ref="AF58:AK58"/>
-    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="AF60:AK60"/>
-    <mergeCell ref="B99:AK99"/>
     <mergeCell ref="AC49:AE49"/>
     <mergeCell ref="AC36:AE36"/>
     <mergeCell ref="Y35:AB35"/>
@@ -11361,6 +11323,7 @@
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="C123:AK123"/>
     <mergeCell ref="C110:AK110"/>
+    <mergeCell ref="B80:I80"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
